--- a/文档及测试数据/抵押登记台账.xlsx
+++ b/文档及测试数据/抵押登记台账.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LCY\AppData\Roaming\SPB_Data\gitee\auto-work\AutoBdc\py\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LCY\AppData\Roaming\SPB_Data\gitee\auto-work\文档及测试数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932B8888-7270-4A4E-9E4F-2CE2FD8561B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4DE054-4640-49D0-A039-6FBD873341D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13710" yWindow="3930" windowWidth="21945" windowHeight="14100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14355" yWindow="5475" windowWidth="21945" windowHeight="14100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="预告抵押（合并登记）" sheetId="3" r:id="rId1"/>
     <sheet name="新系统业务" sheetId="2" r:id="rId2"/>
     <sheet name="旧系统业务" sheetId="1" r:id="rId3"/>
+    <sheet name="业务类型及所需材料" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9971" uniqueCount="6574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9991" uniqueCount="6589">
   <si>
     <t>登记业务号</t>
   </si>
@@ -21862,6 +21863,65 @@
     <t>0</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>预告抵押</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不动产登记申请书</t>
+  </si>
+  <si>
+    <t>不动产抵押登记询问笔录</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>申请人身份证明</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>委托函</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不动产抵押权注销证明</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>借款合同</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵押合同</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>房产证</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不动产登记证明</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品房预售合同</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>关于抵押预告登记的约定</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>结婚证或具结保证书</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>求和</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -21870,7 +21930,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -21895,6 +21955,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -21956,7 +22022,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -22061,6 +22127,18 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -22772,13 +22850,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="表4" displayName="表4" ref="A1:N981" totalsRowShown="0">
-  <autoFilter ref="A1:N981" xr:uid="{00000000-0009-0000-0100-000004000000}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="转本登记（预告转正式）"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N981" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="登记业务号" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="抵押人1" dataDxfId="21"/>
@@ -29901,7 +29973,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="15" t="s">
         <v>502</v>
       </c>
@@ -29955,7 +30027,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="15" t="s">
         <v>513</v>
       </c>
@@ -30011,7 +30083,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="15" t="s">
         <v>521</v>
       </c>
@@ -30065,7 +30137,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="15" t="s">
         <v>530</v>
       </c>
@@ -30113,7 +30185,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="15" t="s">
         <v>537</v>
       </c>
@@ -30164,7 +30236,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="15" t="s">
         <v>545</v>
       </c>
@@ -30209,7 +30281,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="15" t="s">
         <v>551</v>
       </c>
@@ -30260,7 +30332,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="15" t="s">
         <v>559</v>
       </c>
@@ -30306,7 +30378,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="15" t="s">
         <v>567</v>
       </c>
@@ -30348,7 +30420,7 @@
         <v>曾红</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="15" t="s">
         <v>572</v>
       </c>
@@ -30390,7 +30462,7 @@
         <v>郭宁</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="15" t="s">
         <v>577</v>
       </c>
@@ -30438,7 +30510,7 @@
         <v>胡红英 李章仁</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="15" t="s">
         <v>584</v>
       </c>
@@ -30480,7 +30552,7 @@
         <v>康艳梅</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="15" t="s">
         <v>589</v>
       </c>
@@ -30522,7 +30594,7 @@
         <v>王倩</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="15" t="s">
         <v>594</v>
       </c>
@@ -30570,7 +30642,7 @@
         <v>邹琅 赖平平</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="15" t="s">
         <v>601</v>
       </c>
@@ -30612,7 +30684,7 @@
         <v>匡仁棒</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="15" t="s">
         <v>607</v>
       </c>
@@ -30660,7 +30732,7 @@
         <v>刘志蓉 刘建忠</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="15" t="s">
         <v>614</v>
       </c>
@@ -30708,7 +30780,7 @@
         <v>谢志刚 范兰</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="15" t="s">
         <v>621</v>
       </c>
@@ -30750,7 +30822,7 @@
         <v>戴莹</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="15" t="s">
         <v>626</v>
       </c>
@@ -30792,7 +30864,7 @@
         <v>郭奇智</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="15" t="s">
         <v>631</v>
       </c>
@@ -30840,7 +30912,7 @@
         <v>郭晓倩 曾圣皆</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="15" t="s">
         <v>638</v>
       </c>
@@ -30888,7 +30960,7 @@
         <v>周军平 廖玉香</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="15" t="s">
         <v>645</v>
       </c>
@@ -30936,7 +31008,7 @@
         <v>孙丽娟 唐斌</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="15" t="s">
         <v>652</v>
       </c>
@@ -30984,7 +31056,7 @@
         <v>刘玲 周九羊</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="15" t="s">
         <v>659</v>
       </c>
@@ -31032,7 +31104,7 @@
         <v>夏晓敏 宋春英</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="15" t="s">
         <v>666</v>
       </c>
@@ -31074,7 +31146,7 @@
         <v>巫秋月</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="15" t="s">
         <v>671</v>
       </c>
@@ -31116,7 +31188,7 @@
         <v>杨美琴</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="15" t="s">
         <v>676</v>
       </c>
@@ -31164,7 +31236,7 @@
         <v>郭红梅 陈立军</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="15" t="s">
         <v>683</v>
       </c>
@@ -31212,7 +31284,7 @@
         <v>周庆初 罗林林</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="15" t="s">
         <v>690</v>
       </c>
@@ -31260,7 +31332,7 @@
         <v>罗吉祥 张丹</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="15" t="s">
         <v>697</v>
       </c>
@@ -31308,7 +31380,7 @@
         <v>曾爱萍 张莉花</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="15" t="s">
         <v>704</v>
       </c>
@@ -31356,7 +31428,7 @@
         <v>王小丁 肖有志</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="15" t="s">
         <v>711</v>
       </c>
@@ -31404,7 +31476,7 @@
         <v>周志强 姜语</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="15" t="s">
         <v>718</v>
       </c>
@@ -31446,7 +31518,7 @@
         <v>朱博琨</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="15" t="s">
         <v>723</v>
       </c>
@@ -31494,7 +31566,7 @@
         <v>晏勇 廖彩琴</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="15" t="s">
         <v>730</v>
       </c>
@@ -31542,7 +31614,7 @@
         <v>黄先庆 黄翠</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="15" t="s">
         <v>737</v>
       </c>
@@ -31590,7 +31662,7 @@
         <v>宁淑娟 曾勇辉</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="15" t="s">
         <v>744</v>
       </c>
@@ -31632,7 +31704,7 @@
         <v>刘翰阳</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="15" t="s">
         <v>749</v>
       </c>
@@ -31680,7 +31752,7 @@
         <v>罗桃根 赖露萍</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="15" t="s">
         <v>756</v>
       </c>
@@ -31722,7 +31794,7 @@
         <v>张益</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="15" t="s">
         <v>762</v>
       </c>
@@ -31770,7 +31842,7 @@
         <v>黄称龙 罗海珍</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="15" t="s">
         <v>769</v>
       </c>
@@ -31818,7 +31890,7 @@
         <v>周文宏 吴快乐</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="15" t="s">
         <v>776</v>
       </c>
@@ -31866,7 +31938,7 @@
         <v>朱适誉 盛水兵</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="15" t="s">
         <v>783</v>
       </c>
@@ -31914,7 +31986,7 @@
         <v>虞永梅 李良启</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="15" t="s">
         <v>790</v>
       </c>
@@ -31962,7 +32034,7 @@
         <v>王星 周萍华</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="15" t="s">
         <v>797</v>
       </c>
@@ -32004,7 +32076,7 @@
         <v>张建金</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="15" t="s">
         <v>802</v>
       </c>
@@ -32046,7 +32118,7 @@
         <v>邓炳秀</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="15" t="s">
         <v>807</v>
       </c>
@@ -32094,7 +32166,7 @@
         <v>邓卫平 廖昔君</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="15" t="s">
         <v>814</v>
       </c>
@@ -32136,7 +32208,7 @@
         <v>李丽丹</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="15" t="s">
         <v>820</v>
       </c>
@@ -32184,7 +32256,7 @@
         <v>陈秋平 杨学苗</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="15" t="s">
         <v>827</v>
       </c>
@@ -32232,7 +32304,7 @@
         <v>朱晓辉 陈志鑫</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="15" t="s">
         <v>834</v>
       </c>
@@ -32274,7 +32346,7 @@
         <v>周小飞</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="15" t="s">
         <v>839</v>
       </c>
@@ -32322,7 +32394,7 @@
         <v>张高桂 李龙飞</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="15" t="s">
         <v>846</v>
       </c>
@@ -32370,7 +32442,7 @@
         <v>戴彬 邓晓燕</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="15" t="s">
         <v>853</v>
       </c>
@@ -32418,7 +32490,7 @@
         <v>黄月兰 王昭云</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="15" t="s">
         <v>860</v>
       </c>
@@ -32466,7 +32538,7 @@
         <v>戴林堂 王江苹</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="15" t="s">
         <v>868</v>
       </c>
@@ -32514,7 +32586,7 @@
         <v>谢云 肖勇水</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="15" t="s">
         <v>875</v>
       </c>
@@ -32562,7 +32634,7 @@
         <v>罗涛 郭清清</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="15" t="s">
         <v>882</v>
       </c>
@@ -32608,7 +32680,7 @@
         <v>杨晨 刘玲</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="15" t="s">
         <v>888</v>
       </c>
@@ -32650,7 +32722,7 @@
         <v>王万超</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="15" t="s">
         <v>894</v>
       </c>
@@ -32698,7 +32770,7 @@
         <v>夏侯佐迩 何燕</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="15" t="s">
         <v>901</v>
       </c>
@@ -32740,7 +32812,7 @@
         <v>欧阳回清</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="15" t="s">
         <v>907</v>
       </c>
@@ -32782,7 +32854,7 @@
         <v>罗富勇</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="15" t="s">
         <v>912</v>
       </c>
@@ -32876,7 +32948,7 @@
         <v>周六姑 刘足华</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="15" t="s">
         <v>921</v>
       </c>
@@ -32924,7 +32996,7 @@
         <v>吴桂花 吴维立</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="15" t="s">
         <v>928</v>
       </c>
@@ -32972,7 +33044,7 @@
         <v>肖文星 王龙</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="15" t="s">
         <v>935</v>
       </c>
@@ -33020,7 +33092,7 @@
         <v>梁崇焕 郭星</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="15" t="s">
         <v>942</v>
       </c>
@@ -33062,7 +33134,7 @@
         <v>熊春妹</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="15" t="s">
         <v>947</v>
       </c>
@@ -33110,7 +33182,7 @@
         <v>罗跃华 王春兰</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="15" t="s">
         <v>954</v>
       </c>
@@ -33152,7 +33224,7 @@
         <v>杨文清</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="15" t="s">
         <v>960</v>
       </c>
@@ -33188,7 +33260,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="15" t="s">
         <v>964</v>
       </c>
@@ -33236,7 +33308,7 @@
         <v>朱小兵 郭月媛</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="15" t="s">
         <v>971</v>
       </c>
@@ -33276,7 +33348,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="15" t="s">
         <v>977</v>
       </c>
@@ -33324,7 +33396,7 @@
         <v>钟姗姗 张汉清</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="15" t="s">
         <v>984</v>
       </c>
@@ -33372,7 +33444,7 @@
         <v>何居贵 杨香兰 何显照</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="15" t="s">
         <v>992</v>
       </c>
@@ -33420,7 +33492,7 @@
         <v>黎凤 李卫</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="15" t="s">
         <v>999</v>
       </c>
@@ -33468,7 +33540,7 @@
         <v>管美玲 旷有博</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="15" t="s">
         <v>1006</v>
       </c>
@@ -33506,7 +33578,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="15" t="s">
         <v>1011</v>
       </c>
@@ -33546,7 +33618,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="15" t="s">
         <v>1017</v>
       </c>
@@ -33586,7 +33658,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="15" t="s">
         <v>1023</v>
       </c>
@@ -33626,7 +33698,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="15" t="s">
         <v>1029</v>
       </c>
@@ -33666,7 +33738,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="15" t="s">
         <v>1035</v>
       </c>
@@ -33714,7 +33786,7 @@
         <v>王强 潘洋琼</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="15" t="s">
         <v>1043</v>
       </c>
@@ -33756,7 +33828,7 @@
         <v>刘星</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="15" t="s">
         <v>1048</v>
       </c>
@@ -33802,7 +33874,7 @@
         <v>黄嫩 周毅</v>
       </c>
     </row>
-    <row r="87" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="15" t="s">
         <v>1055</v>
       </c>
@@ -33842,7 +33914,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="15" t="s">
         <v>1061</v>
       </c>
@@ -33882,7 +33954,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="15" t="s">
         <v>1067</v>
       </c>
@@ -33922,7 +33994,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="15" t="s">
         <v>1073</v>
       </c>
@@ -33970,7 +34042,7 @@
         <v>杨黎君 罗惟银</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="15" t="s">
         <v>1077</v>
       </c>
@@ -34010,7 +34082,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="15" t="s">
         <v>1083</v>
       </c>
@@ -34048,7 +34120,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="15" t="s">
         <v>1089</v>
       </c>
@@ -34096,7 +34168,7 @@
         <v>刘佳丽 曾建</v>
       </c>
     </row>
-    <row r="94" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="15" t="s">
         <v>1096</v>
       </c>
@@ -34138,7 +34210,7 @@
         <v>彭婧</v>
       </c>
     </row>
-    <row r="95" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="15" t="s">
         <v>1101</v>
       </c>
@@ -34180,7 +34252,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="15" t="s">
         <v>1107</v>
       </c>
@@ -34220,7 +34292,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="15" t="s">
         <v>1113</v>
       </c>
@@ -34268,7 +34340,7 @@
         <v>杨浪开 肖清花</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="15" t="s">
         <v>1115</v>
       </c>
@@ -34316,7 +34388,7 @@
         <v>蒋妍妮 郭君明</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="15" t="s">
         <v>1122</v>
       </c>
@@ -34364,7 +34436,7 @@
         <v>高永玲 李艳</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="15" t="s">
         <v>1129</v>
       </c>
@@ -34404,7 +34476,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="15" t="s">
         <v>1135</v>
       </c>
@@ -34446,7 +34518,7 @@
         <v>王朋英</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="15" t="s">
         <v>1140</v>
       </c>
@@ -34488,7 +34560,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="15" t="s">
         <v>1146</v>
       </c>
@@ -34524,7 +34596,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="15" t="s">
         <v>1150</v>
       </c>
@@ -34564,7 +34636,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="15" t="s">
         <v>1156</v>
       </c>
@@ -34604,7 +34676,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="15" t="s">
         <v>1162</v>
       </c>
@@ -34644,7 +34716,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="15" t="s">
         <v>1168</v>
       </c>
@@ -34680,7 +34752,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="15" t="s">
         <v>1172</v>
       </c>
@@ -34720,7 +34792,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="15" t="s">
         <v>1178</v>
       </c>
@@ -34760,7 +34832,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="15" t="s">
         <v>1184</v>
       </c>
@@ -34800,7 +34872,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="15" t="s">
         <v>1190</v>
       </c>
@@ -34840,7 +34912,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="15" t="s">
         <v>1196</v>
       </c>
@@ -34876,7 +34948,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="15" t="s">
         <v>1200</v>
       </c>
@@ -34912,7 +34984,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="15" t="s">
         <v>1204</v>
       </c>
@@ -34948,7 +35020,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="15" t="s">
         <v>1208</v>
       </c>
@@ -34988,7 +35060,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="15" t="s">
         <v>1213</v>
       </c>
@@ -35022,7 +35094,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="15" t="s">
         <v>1217</v>
       </c>
@@ -35064,7 +35136,7 @@
         <v>喻敏</v>
       </c>
     </row>
-    <row r="118" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="15" t="s">
         <v>1222</v>
       </c>
@@ -35106,7 +35178,7 @@
         <v>周宏华</v>
       </c>
     </row>
-    <row r="119" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="15" t="s">
         <v>1227</v>
       </c>
@@ -35148,7 +35220,7 @@
         <v>肖蒙恩</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="15" t="s">
         <v>1233</v>
       </c>
@@ -35188,7 +35260,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="15" t="s">
         <v>1239</v>
       </c>
@@ -35224,7 +35296,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="15" t="s">
         <v>1242</v>
       </c>
@@ -35264,7 +35336,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="15" t="s">
         <v>1248</v>
       </c>
@@ -35300,7 +35372,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="15" t="s">
         <v>1252</v>
       </c>
@@ -35340,7 +35412,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="15" t="s">
         <v>1258</v>
       </c>
@@ -35388,7 +35460,7 @@
         <v>吴花秀 范观音</v>
       </c>
     </row>
-    <row r="126" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="15" t="s">
         <v>1265</v>
       </c>
@@ -35436,7 +35508,7 @@
         <v>刘晶 余刚</v>
       </c>
     </row>
-    <row r="127" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="15" t="s">
         <v>1272</v>
       </c>
@@ -35478,7 +35550,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="15" t="s">
         <v>1279</v>
       </c>
@@ -35526,7 +35598,7 @@
         <v>王红平 宋润秀</v>
       </c>
     </row>
-    <row r="129" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="15" t="s">
         <v>1286</v>
       </c>
@@ -35568,7 +35640,7 @@
         <v>徐燕</v>
       </c>
     </row>
-    <row r="130" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="15" t="s">
         <v>1291</v>
       </c>
@@ -35616,7 +35688,7 @@
         <v>肖祖烈 王美香</v>
       </c>
     </row>
-    <row r="131" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="15" t="s">
         <v>1298</v>
       </c>
@@ -35664,7 +35736,7 @@
         <v>章荣杰 黄冬兰</v>
       </c>
     </row>
-    <row r="132" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="15" t="s">
         <v>1301</v>
       </c>
@@ -35712,7 +35784,7 @@
         <v>王林非 秦文确</v>
       </c>
     </row>
-    <row r="133" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="15" t="s">
         <v>1308</v>
       </c>
@@ -35760,7 +35832,7 @@
         <v>刘青 朱梦杨</v>
       </c>
     </row>
-    <row r="134" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="15" t="s">
         <v>1315</v>
       </c>
@@ -35800,7 +35872,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="15" t="s">
         <v>1321</v>
       </c>
@@ -35842,7 +35914,7 @@
         <v>李菊香</v>
       </c>
     </row>
-    <row r="136" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="15" t="s">
         <v>1326</v>
       </c>
@@ -35884,7 +35956,7 @@
         <v>李智寿</v>
       </c>
     </row>
-    <row r="137" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="15" t="s">
         <v>1331</v>
       </c>
@@ -35920,7 +35992,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="15" t="s">
         <v>1335</v>
       </c>
@@ -35960,7 +36032,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="15" t="s">
         <v>1342</v>
       </c>
@@ -36000,7 +36072,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="15" t="s">
         <v>1348</v>
       </c>
@@ -36040,7 +36112,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="15" t="s">
         <v>1354</v>
       </c>
@@ -36080,7 +36152,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="15" t="s">
         <v>1360</v>
       </c>
@@ -36116,7 +36188,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="15" t="s">
         <v>1364</v>
       </c>
@@ -36164,7 +36236,7 @@
         <v>李招华 王其光</v>
       </c>
     </row>
-    <row r="144" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="15" t="s">
         <v>1371</v>
       </c>
@@ -36200,7 +36272,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="15" t="s">
         <v>1375</v>
       </c>
@@ -36236,7 +36308,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="15" t="s">
         <v>1379</v>
       </c>
@@ -36272,7 +36344,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="15" t="s">
         <v>1381</v>
       </c>
@@ -36314,7 +36386,7 @@
         <v>李媛媛</v>
       </c>
     </row>
-    <row r="148" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="15" t="s">
         <v>1386</v>
       </c>
@@ -36350,7 +36422,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="15" t="s">
         <v>1390</v>
       </c>
@@ -36392,7 +36464,7 @@
         <v>郭亮</v>
       </c>
     </row>
-    <row r="150" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="15" t="s">
         <v>1392</v>
       </c>
@@ -36440,7 +36512,7 @@
         <v>吴海庆 罗金珍</v>
       </c>
     </row>
-    <row r="151" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="15" t="s">
         <v>1399</v>
       </c>
@@ -36488,7 +36560,7 @@
         <v>陈小娥 朱禄文</v>
       </c>
     </row>
-    <row r="152" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="15" t="s">
         <v>1406</v>
       </c>
@@ -36536,7 +36608,7 @@
         <v>曾小明 何宝玲</v>
       </c>
     </row>
-    <row r="153" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="15" t="s">
         <v>1413</v>
       </c>
@@ -36576,7 +36648,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="15" t="s">
         <v>1419</v>
       </c>
@@ -36624,7 +36696,7 @@
         <v>郭洁洁 贺其铮</v>
       </c>
     </row>
-    <row r="155" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="15" t="s">
         <v>1426</v>
       </c>
@@ -36666,7 +36738,7 @@
         <v>郭坎</v>
       </c>
     </row>
-    <row r="156" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="15" t="s">
         <v>1431</v>
       </c>
@@ -36712,7 +36784,7 @@
         <v>孙小勇 刘秋莲</v>
       </c>
     </row>
-    <row r="157" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="15" t="s">
         <v>1438</v>
       </c>
@@ -36760,7 +36832,7 @@
         <v>何丹 崔勇</v>
       </c>
     </row>
-    <row r="158" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="15" t="s">
         <v>1445</v>
       </c>
@@ -36808,7 +36880,7 @@
         <v>万云强 刘兰</v>
       </c>
     </row>
-    <row r="159" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="15" t="s">
         <v>1447</v>
       </c>
@@ -36844,7 +36916,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="15" t="s">
         <v>1451</v>
       </c>
@@ -36884,7 +36956,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="15" t="s">
         <v>1457</v>
       </c>
@@ -36924,7 +36996,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="15" t="s">
         <v>1463</v>
       </c>
@@ -36960,7 +37032,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="15" t="s">
         <v>1467</v>
       </c>
@@ -37000,7 +37072,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="15" t="s">
         <v>1473</v>
       </c>
@@ -37038,7 +37110,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="15" t="s">
         <v>1478</v>
       </c>
@@ -37074,7 +37146,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="15" t="s">
         <v>1482</v>
       </c>
@@ -37114,7 +37186,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="15" t="s">
         <v>1488</v>
       </c>
@@ -37150,7 +37222,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="15" t="s">
         <v>1492</v>
       </c>
@@ -37196,7 +37268,7 @@
         <v>李渊 周媛华</v>
       </c>
     </row>
-    <row r="169" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="15" t="s">
         <v>1499</v>
       </c>
@@ -37242,7 +37314,7 @@
         <v>郭敏 曾志清</v>
       </c>
     </row>
-    <row r="170" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="15" t="s">
         <v>1506</v>
       </c>
@@ -37284,7 +37356,7 @@
         <v>郭芮彤</v>
       </c>
     </row>
-    <row r="171" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="15" t="s">
         <v>1511</v>
       </c>
@@ -37324,7 +37396,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="15" t="s">
         <v>1517</v>
       </c>
@@ -37364,7 +37436,7 @@
         <v/>
       </c>
     </row>
-    <row r="173" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="15" t="s">
         <v>1523</v>
       </c>
@@ -37450,7 +37522,7 @@
         <v>周小勇 杨珍丽</v>
       </c>
     </row>
-    <row r="175" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="15" t="s">
         <v>1532</v>
       </c>
@@ -37490,7 +37562,7 @@
         <v/>
       </c>
     </row>
-    <row r="176" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="15" t="s">
         <v>1538</v>
       </c>
@@ -37530,7 +37602,7 @@
         <v/>
       </c>
     </row>
-    <row r="177" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="15" t="s">
         <v>1544</v>
       </c>
@@ -37566,7 +37638,7 @@
         <v/>
       </c>
     </row>
-    <row r="178" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="15" t="s">
         <v>1548</v>
       </c>
@@ -37606,7 +37678,7 @@
         <v/>
       </c>
     </row>
-    <row r="179" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="15" t="s">
         <v>1554</v>
       </c>
@@ -37646,7 +37718,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="15" t="s">
         <v>1560</v>
       </c>
@@ -37682,7 +37754,7 @@
         <v/>
       </c>
     </row>
-    <row r="181" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="15" t="s">
         <v>1564</v>
       </c>
@@ -37718,7 +37790,7 @@
         <v/>
       </c>
     </row>
-    <row r="182" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="15" t="s">
         <v>1568</v>
       </c>
@@ -37758,7 +37830,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="15" t="s">
         <v>1574</v>
       </c>
@@ -37802,7 +37874,7 @@
         <v>刘桂林 刘琼</v>
       </c>
     </row>
-    <row r="184" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="15" t="s">
         <v>1581</v>
       </c>
@@ -37890,7 +37962,7 @@
         <v>王纯有 郭小红</v>
       </c>
     </row>
-    <row r="186" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="15" t="s">
         <v>1595</v>
       </c>
@@ -37934,7 +38006,7 @@
         <v>吴才旺 吴莉</v>
       </c>
     </row>
-    <row r="187" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="15" t="s">
         <v>1602</v>
       </c>
@@ -37982,7 +38054,7 @@
         <v>姚通 范淑慧</v>
       </c>
     </row>
-    <row r="188" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="15" t="s">
         <v>1604</v>
       </c>
@@ -38022,7 +38094,7 @@
         <v/>
       </c>
     </row>
-    <row r="189" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="15" t="s">
         <v>1610</v>
       </c>
@@ -38070,7 +38142,7 @@
         <v>曾安邦 郭安珍</v>
       </c>
     </row>
-    <row r="190" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="15" t="s">
         <v>1617</v>
       </c>
@@ -38118,7 +38190,7 @@
         <v>赖红梅 胡青</v>
       </c>
     </row>
-    <row r="191" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191" s="15" t="s">
         <v>1624</v>
       </c>
@@ -38164,7 +38236,7 @@
         <v>杨菊蓉 郭春亮</v>
       </c>
     </row>
-    <row r="192" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="15" t="s">
         <v>1631</v>
       </c>
@@ -38202,7 +38274,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="15" t="s">
         <v>1636</v>
       </c>
@@ -38244,7 +38316,7 @@
         <v>钟恩华</v>
       </c>
     </row>
-    <row r="194" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="15" t="s">
         <v>1642</v>
       </c>
@@ -38280,7 +38352,7 @@
         <v/>
       </c>
     </row>
-    <row r="195" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="15" t="s">
         <v>1646</v>
       </c>
@@ -38320,7 +38392,7 @@
         <v/>
       </c>
     </row>
-    <row r="196" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="15" t="s">
         <v>1652</v>
       </c>
@@ -38360,7 +38432,7 @@
         <v/>
       </c>
     </row>
-    <row r="197" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="15" t="s">
         <v>1658</v>
       </c>
@@ -38396,7 +38468,7 @@
         <v/>
       </c>
     </row>
-    <row r="198" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="15" t="s">
         <v>1662</v>
       </c>
@@ -38436,7 +38508,7 @@
         <v/>
       </c>
     </row>
-    <row r="199" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="15" t="s">
         <v>1668</v>
       </c>
@@ -38474,7 +38546,7 @@
         <v/>
       </c>
     </row>
-    <row r="200" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="15" t="s">
         <v>1673</v>
       </c>
@@ -38510,7 +38582,7 @@
         <v/>
       </c>
     </row>
-    <row r="201" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="15" t="s">
         <v>1677</v>
       </c>
@@ -38550,7 +38622,7 @@
         <v/>
       </c>
     </row>
-    <row r="202" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="15" t="s">
         <v>1683</v>
       </c>
@@ -38594,7 +38666,7 @@
         <v>温火丽 彭宁斌</v>
       </c>
     </row>
-    <row r="203" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="15" t="s">
         <v>1690</v>
       </c>
@@ -38642,7 +38714,7 @@
         <v>罗春华 袁淑珍</v>
       </c>
     </row>
-    <row r="204" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="15" t="s">
         <v>1693</v>
       </c>
@@ -38690,7 +38762,7 @@
         <v>罗春华 袁淑珍</v>
       </c>
     </row>
-    <row r="205" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="15" t="s">
         <v>1695</v>
       </c>
@@ -38738,7 +38810,7 @@
         <v>罗春华 袁淑珍</v>
       </c>
     </row>
-    <row r="206" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="15" t="s">
         <v>1697</v>
       </c>
@@ -38774,7 +38846,7 @@
         <v/>
       </c>
     </row>
-    <row r="207" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="15" t="s">
         <v>1701</v>
       </c>
@@ -38818,7 +38890,7 @@
         <v>张晓龙 周彤彤</v>
       </c>
     </row>
-    <row r="208" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="15" t="s">
         <v>1708</v>
       </c>
@@ -38860,7 +38932,7 @@
         <v/>
       </c>
     </row>
-    <row r="209" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="15" t="s">
         <v>1714</v>
       </c>
@@ -38902,7 +38974,7 @@
         <v>刘文涛</v>
       </c>
     </row>
-    <row r="210" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="15" t="s">
         <v>1719</v>
       </c>
@@ -38942,7 +39014,7 @@
         <v/>
       </c>
     </row>
-    <row r="211" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="15" t="s">
         <v>1725</v>
       </c>
@@ -38988,7 +39060,7 @@
         <v>龙轩 刘华美</v>
       </c>
     </row>
-    <row r="212" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="15" t="s">
         <v>1732</v>
       </c>
@@ -39036,7 +39108,7 @@
         <v>郭必塬 彭小妹</v>
       </c>
     </row>
-    <row r="213" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="15" t="s">
         <v>1739</v>
       </c>
@@ -39080,7 +39152,7 @@
         <v>曾昭君 陈曦</v>
       </c>
     </row>
-    <row r="214" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="15" t="s">
         <v>1746</v>
       </c>
@@ -39122,7 +39194,7 @@
         <v>罗小花</v>
       </c>
     </row>
-    <row r="215" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="15" t="s">
         <v>1751</v>
       </c>
@@ -39170,7 +39242,7 @@
         <v>曾洪 卢江华</v>
       </c>
     </row>
-    <row r="216" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="15" t="s">
         <v>1754</v>
       </c>
@@ -39216,7 +39288,7 @@
         <v>蒋兰华 陈国华</v>
       </c>
     </row>
-    <row r="217" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="18" t="s">
         <v>1757</v>
       </c>
@@ -39264,7 +39336,7 @@
         <v>曹胜智 谢雪峰</v>
       </c>
     </row>
-    <row r="218" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218" s="15" t="s">
         <v>1764</v>
       </c>
@@ -39304,7 +39376,7 @@
         <v/>
       </c>
     </row>
-    <row r="219" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219" s="15" t="s">
         <v>1770</v>
       </c>
@@ -39344,7 +39416,7 @@
         <v/>
       </c>
     </row>
-    <row r="220" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220" s="15" t="s">
         <v>1776</v>
       </c>
@@ -39386,7 +39458,7 @@
         <v/>
       </c>
     </row>
-    <row r="221" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221" s="15" t="s">
         <v>1777</v>
       </c>
@@ -39426,7 +39498,7 @@
         <v/>
       </c>
     </row>
-    <row r="222" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222" s="15" t="s">
         <v>1783</v>
       </c>
@@ -39462,7 +39534,7 @@
         <v/>
       </c>
     </row>
-    <row r="223" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A223" s="15" t="s">
         <v>1787</v>
       </c>
@@ -39508,7 +39580,7 @@
         <v>毛智文 杜玉梅</v>
       </c>
     </row>
-    <row r="224" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A224" s="15" t="s">
         <v>1794</v>
       </c>
@@ -39550,7 +39622,7 @@
         <v>熊丹琪</v>
       </c>
     </row>
-    <row r="225" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A225" s="15" t="s">
         <v>1799</v>
       </c>
@@ -39586,7 +39658,7 @@
         <v/>
       </c>
     </row>
-    <row r="226" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226" s="15" t="s">
         <v>1803</v>
       </c>
@@ -39634,7 +39706,7 @@
         <v>何文祥 吴芳</v>
       </c>
     </row>
-    <row r="227" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227" s="15" t="s">
         <v>1810</v>
       </c>
@@ -39682,7 +39754,7 @@
         <v>陈仕斌 肖琼</v>
       </c>
     </row>
-    <row r="228" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="15" t="s">
         <v>1817</v>
       </c>
@@ -39724,7 +39796,7 @@
         <v/>
       </c>
     </row>
-    <row r="229" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="15" t="s">
         <v>1823</v>
       </c>
@@ -39764,7 +39836,7 @@
         <v/>
       </c>
     </row>
-    <row r="230" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230" s="15" t="s">
         <v>1829</v>
       </c>
@@ -39804,7 +39876,7 @@
         <v/>
       </c>
     </row>
-    <row r="231" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231" s="15" t="s">
         <v>1835</v>
       </c>
@@ -39840,7 +39912,7 @@
         <v/>
       </c>
     </row>
-    <row r="232" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="15" t="s">
         <v>1838</v>
       </c>
@@ -39880,7 +39952,7 @@
         <v/>
       </c>
     </row>
-    <row r="233" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233" s="15" t="s">
         <v>1844</v>
       </c>
@@ -39918,7 +39990,7 @@
         <v/>
       </c>
     </row>
-    <row r="234" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A234" s="15" t="s">
         <v>1849</v>
       </c>
@@ -39956,7 +40028,7 @@
         <v/>
       </c>
     </row>
-    <row r="235" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235" s="15" t="s">
         <v>1854</v>
       </c>
@@ -39998,7 +40070,7 @@
         <v>李伊丽</v>
       </c>
     </row>
-    <row r="236" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236" s="15" t="s">
         <v>1859</v>
       </c>
@@ -40044,7 +40116,7 @@
         <v>尚娟 贺勇华</v>
       </c>
     </row>
-    <row r="237" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237" s="6" t="s">
         <v>1866</v>
       </c>
@@ -40082,7 +40154,7 @@
         <v/>
       </c>
     </row>
-    <row r="238" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238" s="15" t="s">
         <v>1871</v>
       </c>
@@ -40118,7 +40190,7 @@
         <v/>
       </c>
     </row>
-    <row r="239" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="15" t="s">
         <v>1875</v>
       </c>
@@ -40194,7 +40266,7 @@
         <v>李丹</v>
       </c>
     </row>
-    <row r="241" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A241" s="15" t="s">
         <v>1885</v>
       </c>
@@ -40234,7 +40306,7 @@
         <v/>
       </c>
     </row>
-    <row r="242" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="15" t="s">
         <v>1891</v>
       </c>
@@ -40274,7 +40346,7 @@
         <v/>
       </c>
     </row>
-    <row r="243" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243" s="15" t="s">
         <v>1897</v>
       </c>
@@ -40310,7 +40382,7 @@
         <v/>
       </c>
     </row>
-    <row r="244" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244" s="15" t="s">
         <v>1901</v>
       </c>
@@ -40346,7 +40418,7 @@
         <v/>
       </c>
     </row>
-    <row r="245" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245" s="15" t="s">
         <v>1905</v>
       </c>
@@ -40388,7 +40460,7 @@
         <v>彭钟华</v>
       </c>
     </row>
-    <row r="246" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A246" s="15" t="s">
         <v>1910</v>
       </c>
@@ -40434,7 +40506,7 @@
         <v>田小洋 曹金红</v>
       </c>
     </row>
-    <row r="247" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247" s="15" t="s">
         <v>1912</v>
       </c>
@@ -40480,7 +40552,7 @@
         <v>肖敏华 刘文斌</v>
       </c>
     </row>
-    <row r="248" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248" s="15" t="s">
         <v>1919</v>
       </c>
@@ -40522,7 +40594,7 @@
         <v>曾圣堪</v>
       </c>
     </row>
-    <row r="249" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249" s="15" t="s">
         <v>1924</v>
       </c>
@@ -40568,7 +40640,7 @@
         <v>张紫薇 钟恩华</v>
       </c>
     </row>
-    <row r="250" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="15" t="s">
         <v>1929</v>
       </c>
@@ -40610,7 +40682,7 @@
         <v>徐丽</v>
       </c>
     </row>
-    <row r="251" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="15" t="s">
         <v>1934</v>
       </c>
@@ -40652,7 +40724,7 @@
         <v>范孝兴</v>
       </c>
     </row>
-    <row r="252" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="15" t="s">
         <v>1939</v>
       </c>
@@ -40700,7 +40772,7 @@
         <v>刘红梅 王建勇</v>
       </c>
     </row>
-    <row r="253" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253" s="15" t="s">
         <v>1946</v>
       </c>
@@ -40742,7 +40814,7 @@
         <v>欧阳思</v>
       </c>
     </row>
-    <row r="254" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A254" s="15" t="s">
         <v>1951</v>
       </c>
@@ -40784,7 +40856,7 @@
         <v>朱志勇</v>
       </c>
     </row>
-    <row r="255" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="15" t="s">
         <v>1956</v>
       </c>
@@ -40872,7 +40944,7 @@
         <v>杨凤飞</v>
       </c>
     </row>
-    <row r="257" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="15" t="s">
         <v>1968</v>
       </c>
@@ -40920,7 +40992,7 @@
         <v>肖明坊 曾小娟</v>
       </c>
     </row>
-    <row r="258" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="15" t="s">
         <v>1975</v>
       </c>
@@ -40962,7 +41034,7 @@
         <v>曾凡曦</v>
       </c>
     </row>
-    <row r="259" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="15" t="s">
         <v>1980</v>
       </c>
@@ -41010,7 +41082,7 @@
         <v>朱亚玲 赖平洋</v>
       </c>
     </row>
-    <row r="260" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260" s="15" t="s">
         <v>1987</v>
       </c>
@@ -41058,7 +41130,7 @@
         <v>李刚 阮丽琼</v>
       </c>
     </row>
-    <row r="261" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261" s="15" t="s">
         <v>1994</v>
       </c>
@@ -41098,7 +41170,7 @@
         <v>徐子豪</v>
       </c>
     </row>
-    <row r="262" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="15" t="s">
         <v>1999</v>
       </c>
@@ -41132,7 +41204,7 @@
         <v/>
       </c>
     </row>
-    <row r="263" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="15" t="s">
         <v>2003</v>
       </c>
@@ -41174,7 +41246,7 @@
         <v/>
       </c>
     </row>
-    <row r="264" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A264" s="15" t="s">
         <v>2009</v>
       </c>
@@ -41214,7 +41286,7 @@
         <v/>
       </c>
     </row>
-    <row r="265" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265" s="15" t="s">
         <v>2015</v>
       </c>
@@ -41250,7 +41322,7 @@
         <v/>
       </c>
     </row>
-    <row r="266" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A266" s="15" t="s">
         <v>2019</v>
       </c>
@@ -41290,7 +41362,7 @@
         <v/>
       </c>
     </row>
-    <row r="267" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A267" s="15" t="s">
         <v>2025</v>
       </c>
@@ -41336,7 +41408,7 @@
         <v>曾美琴 郭聪聪</v>
       </c>
     </row>
-    <row r="268" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268" s="15" t="s">
         <v>2032</v>
       </c>
@@ -41376,7 +41448,7 @@
         <v/>
       </c>
     </row>
-    <row r="269" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A269" s="15" t="s">
         <v>2033</v>
       </c>
@@ -41416,7 +41488,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="15" t="s">
         <v>2039</v>
       </c>
@@ -41452,7 +41524,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271" s="15" t="s">
         <v>2043</v>
       </c>
@@ -41492,7 +41564,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A272" s="15" t="s">
         <v>2049</v>
       </c>
@@ -41532,7 +41604,7 @@
         <v/>
       </c>
     </row>
-    <row r="273" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A273" s="15" t="s">
         <v>2055</v>
       </c>
@@ -41572,7 +41644,7 @@
         <v>裴超元</v>
       </c>
     </row>
-    <row r="274" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A274" s="15" t="s">
         <v>2060</v>
       </c>
@@ -41620,7 +41692,7 @@
         <v>刘辛蔚 许伟梅</v>
       </c>
     </row>
-    <row r="275" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A275" s="15" t="s">
         <v>2067</v>
       </c>
@@ -41668,7 +41740,7 @@
         <v>周丽萍 邱礼水</v>
       </c>
     </row>
-    <row r="276" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A276" s="15" t="s">
         <v>2074</v>
       </c>
@@ -41714,7 +41786,7 @@
         <v>欧阳珍珠 王小坤</v>
       </c>
     </row>
-    <row r="277" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A277" s="15" t="s">
         <v>2081</v>
       </c>
@@ -41756,7 +41828,7 @@
         <v>魏丽萍</v>
       </c>
     </row>
-    <row r="278" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A278" s="15" t="s">
         <v>2083</v>
       </c>
@@ -41798,7 +41870,7 @@
         <v>曾宪福</v>
       </c>
     </row>
-    <row r="279" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A279" s="15" t="s">
         <v>2088</v>
       </c>
@@ -41832,7 +41904,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A280" s="15" t="s">
         <v>2091</v>
       </c>
@@ -41872,7 +41944,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A281" s="15" t="s">
         <v>2097</v>
       </c>
@@ -41912,7 +41984,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282" s="15" t="s">
         <v>2103</v>
       </c>
@@ -41952,7 +42024,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A283" s="15" t="s">
         <v>2109</v>
       </c>
@@ -41992,7 +42064,7 @@
         <v/>
       </c>
     </row>
-    <row r="284" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284" s="15" t="s">
         <v>2115</v>
       </c>
@@ -42030,7 +42102,7 @@
         <v/>
       </c>
     </row>
-    <row r="285" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A285" s="15" t="s">
         <v>2120</v>
       </c>
@@ -42070,7 +42142,7 @@
         <v/>
       </c>
     </row>
-    <row r="286" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A286" s="15" t="s">
         <v>2126</v>
       </c>
@@ -42112,7 +42184,7 @@
         <v>宋茜</v>
       </c>
     </row>
-    <row r="287" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A287" s="15" t="s">
         <v>2131</v>
       </c>
@@ -42278,7 +42350,7 @@
         <v>刘文文</v>
       </c>
     </row>
-    <row r="291" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A291" s="15" t="s">
         <v>2153</v>
       </c>
@@ -42320,7 +42392,7 @@
         <v>陈忠财</v>
       </c>
     </row>
-    <row r="292" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A292" s="15" t="s">
         <v>2158</v>
       </c>
@@ -42360,7 +42432,7 @@
         <v>肖惠霞</v>
       </c>
     </row>
-    <row r="293" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A293" s="15" t="s">
         <v>2163</v>
       </c>
@@ -42404,7 +42476,7 @@
         <v>晏元昌 晏志远</v>
       </c>
     </row>
-    <row r="294" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A294" s="15" t="s">
         <v>2170</v>
       </c>
@@ -42452,7 +42524,7 @@
         <v>丘日先 刘招玉</v>
       </c>
     </row>
-    <row r="295" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A295" s="15" t="s">
         <v>2177</v>
       </c>
@@ -42488,7 +42560,7 @@
         <v/>
       </c>
     </row>
-    <row r="296" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A296" s="15" t="s">
         <v>2181</v>
       </c>
@@ -42524,7 +42596,7 @@
         <v/>
       </c>
     </row>
-    <row r="297" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A297" s="15" t="s">
         <v>2185</v>
       </c>
@@ -42570,7 +42642,7 @@
         <v>刘彦 王芬</v>
       </c>
     </row>
-    <row r="298" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A298" s="15" t="s">
         <v>2192</v>
       </c>
@@ -42618,7 +42690,7 @@
         <v>李章银 陈娟</v>
       </c>
     </row>
-    <row r="299" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A299" s="15" t="s">
         <v>2199</v>
       </c>
@@ -42666,7 +42738,7 @@
         <v>李安军 刘正华</v>
       </c>
     </row>
-    <row r="300" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A300" s="15" t="s">
         <v>2207</v>
       </c>
@@ -42708,7 +42780,7 @@
         <v>龚剑</v>
       </c>
     </row>
-    <row r="301" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A301" s="15" t="s">
         <v>2212</v>
       </c>
@@ -42748,7 +42820,7 @@
         <v>王翀</v>
       </c>
     </row>
-    <row r="302" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A302" s="15" t="s">
         <v>2217</v>
       </c>
@@ -42792,7 +42864,7 @@
         <v>田莉 彭彪平</v>
       </c>
     </row>
-    <row r="303" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A303" s="15" t="s">
         <v>2224</v>
       </c>
@@ -42832,7 +42904,7 @@
         <v>王春梅</v>
       </c>
     </row>
-    <row r="304" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A304" s="15" t="s">
         <v>2229</v>
       </c>
@@ -42880,7 +42952,7 @@
         <v>王斌斋 黄琴</v>
       </c>
     </row>
-    <row r="305" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A305" s="15" t="s">
         <v>2236</v>
       </c>
@@ -42916,7 +42988,7 @@
         <v/>
       </c>
     </row>
-    <row r="306" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A306" s="15" t="s">
         <v>2241</v>
       </c>
@@ -42962,7 +43034,7 @@
         <v>胡凤明 朱青凤</v>
       </c>
     </row>
-    <row r="307" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A307" s="15" t="s">
         <v>2248</v>
       </c>
@@ -43006,7 +43078,7 @@
         <v>刘可文 罗艳红</v>
       </c>
     </row>
-    <row r="308" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A308" s="15" t="s">
         <v>2255</v>
       </c>
@@ -43048,7 +43120,7 @@
         <v>何斌</v>
       </c>
     </row>
-    <row r="309" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A309" s="15" t="s">
         <v>2260</v>
       </c>
@@ -43084,7 +43156,7 @@
         <v/>
       </c>
     </row>
-    <row r="310" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A310" s="15" t="s">
         <v>2264</v>
       </c>
@@ -43126,7 +43198,7 @@
         <v>宋必成</v>
       </c>
     </row>
-    <row r="311" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A311" s="15" t="s">
         <v>2269</v>
       </c>
@@ -43168,7 +43240,7 @@
         <v>宋必成</v>
       </c>
     </row>
-    <row r="312" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A312" s="15" t="s">
         <v>2271</v>
       </c>
@@ -43210,7 +43282,7 @@
         <v>宋必成</v>
       </c>
     </row>
-    <row r="313" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A313" s="18" t="s">
         <v>2273</v>
       </c>
@@ -43256,7 +43328,7 @@
         <v>王祥山 徐招莲</v>
       </c>
     </row>
-    <row r="314" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A314" s="18" t="s">
         <v>2273</v>
       </c>
@@ -43302,7 +43374,7 @@
         <v>刘文棹 谢美华</v>
       </c>
     </row>
-    <row r="315" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A315" s="15" t="s">
         <v>2284</v>
       </c>
@@ -43344,7 +43416,7 @@
         <v>彭飞勇</v>
       </c>
     </row>
-    <row r="316" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A316" s="15" t="s">
         <v>2289</v>
       </c>
@@ -43388,7 +43460,7 @@
         <v>刘兰香 陈平云</v>
       </c>
     </row>
-    <row r="317" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A317" s="15" t="s">
         <v>2296</v>
       </c>
@@ -43424,7 +43496,7 @@
         <v/>
       </c>
     </row>
-    <row r="318" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A318" s="15" t="s">
         <v>2297</v>
       </c>
@@ -43464,7 +43536,7 @@
         <v/>
       </c>
     </row>
-    <row r="319" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A319" s="15" t="s">
         <v>2303</v>
       </c>
@@ -43512,7 +43584,7 @@
         <v>李为瑜 胡小青</v>
       </c>
     </row>
-    <row r="320" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A320" s="15" t="s">
         <v>2310</v>
       </c>
@@ -43560,7 +43632,7 @@
         <v>郭涛 胡嘉欣</v>
       </c>
     </row>
-    <row r="321" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A321" s="15" t="s">
         <v>2317</v>
       </c>
@@ -43598,7 +43670,7 @@
         <v/>
       </c>
     </row>
-    <row r="322" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A322" s="15" t="s">
         <v>2321</v>
       </c>
@@ -43638,7 +43710,7 @@
         <v/>
       </c>
     </row>
-    <row r="323" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A323" s="15" t="s">
         <v>2327</v>
       </c>
@@ -43674,7 +43746,7 @@
         <v/>
       </c>
     </row>
-    <row r="324" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A324" s="15" t="s">
         <v>2331</v>
       </c>
@@ -43714,7 +43786,7 @@
         <v/>
       </c>
     </row>
-    <row r="325" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A325" s="15" t="s">
         <v>2337</v>
       </c>
@@ -43752,7 +43824,7 @@
         <v/>
       </c>
     </row>
-    <row r="326" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326" s="15" t="s">
         <v>2342</v>
       </c>
@@ -43792,7 +43864,7 @@
         <v/>
       </c>
     </row>
-    <row r="327" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A327" s="15" t="s">
         <v>2348</v>
       </c>
@@ -43832,7 +43904,7 @@
         <v/>
       </c>
     </row>
-    <row r="328" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A328" s="15" t="s">
         <v>2354</v>
       </c>
@@ -43872,7 +43944,7 @@
         <v/>
       </c>
     </row>
-    <row r="329" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A329" s="15" t="s">
         <v>2360</v>
       </c>
@@ -43912,7 +43984,7 @@
         <v/>
       </c>
     </row>
-    <row r="330" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A330" s="15" t="s">
         <v>2366</v>
       </c>
@@ -43948,7 +44020,7 @@
         <v/>
       </c>
     </row>
-    <row r="331" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A331" s="15" t="s">
         <v>2370</v>
       </c>
@@ -43992,7 +44064,7 @@
         <v>李兵 胡迎龙</v>
       </c>
     </row>
-    <row r="332" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A332" s="15" t="s">
         <v>2377</v>
       </c>
@@ -44038,7 +44110,7 @@
         <v>罗小峰 刘莉</v>
       </c>
     </row>
-    <row r="333" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A333" s="15" t="s">
         <v>2384</v>
       </c>
@@ -44084,7 +44156,7 @@
         <v>罗卫庆 罗美美</v>
       </c>
     </row>
-    <row r="334" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A334" s="15" t="s">
         <v>2391</v>
       </c>
@@ -44120,7 +44192,7 @@
         <v/>
       </c>
     </row>
-    <row r="335" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A335" s="15" t="s">
         <v>2395</v>
       </c>
@@ -44156,7 +44228,7 @@
         <v/>
       </c>
     </row>
-    <row r="336" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A336" s="15" t="s">
         <v>2399</v>
       </c>
@@ -44192,7 +44264,7 @@
         <v/>
       </c>
     </row>
-    <row r="337" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A337" s="15" t="s">
         <v>2403</v>
       </c>
@@ -44232,7 +44304,7 @@
         <v/>
       </c>
     </row>
-    <row r="338" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A338" s="15" t="s">
         <v>2409</v>
       </c>
@@ -44274,7 +44346,7 @@
         <v/>
       </c>
     </row>
-    <row r="339" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="339" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A339" s="15" t="s">
         <v>2415</v>
       </c>
@@ -44314,7 +44386,7 @@
         <v/>
       </c>
     </row>
-    <row r="340" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="340" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A340" s="15" t="s">
         <v>2416</v>
       </c>
@@ -44354,7 +44426,7 @@
         <v/>
       </c>
     </row>
-    <row r="341" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A341" s="15" t="s">
         <v>2422</v>
       </c>
@@ -44394,7 +44466,7 @@
         <v/>
       </c>
     </row>
-    <row r="342" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A342" s="15" t="s">
         <v>2423</v>
       </c>
@@ -44430,7 +44502,7 @@
         <v/>
       </c>
     </row>
-    <row r="343" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A343" s="15" t="s">
         <v>2427</v>
       </c>
@@ -44470,7 +44542,7 @@
         <v/>
       </c>
     </row>
-    <row r="344" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="344" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A344" s="15" t="s">
         <v>2433</v>
       </c>
@@ -44514,7 +44586,7 @@
         <v>吕晨晨 魏磊</v>
       </c>
     </row>
-    <row r="345" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A345" s="15" t="s">
         <v>2440</v>
       </c>
@@ -44556,7 +44628,7 @@
         <v>曹声国</v>
       </c>
     </row>
-    <row r="346" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="346" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A346" s="15" t="s">
         <v>2445</v>
       </c>
@@ -44602,7 +44674,7 @@
         <v>段羊苟 罗玉兰</v>
       </c>
     </row>
-    <row r="347" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A347" s="6" t="s">
         <v>2448</v>
       </c>
@@ -44644,7 +44716,7 @@
         <v>戴鹏</v>
       </c>
     </row>
-    <row r="348" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A348" s="15" t="s">
         <v>2450</v>
       </c>
@@ -44686,7 +44758,7 @@
         <v>张经纶</v>
       </c>
     </row>
-    <row r="349" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="349" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A349" s="15" t="s">
         <v>2455</v>
       </c>
@@ -44728,7 +44800,7 @@
         <v>胡文龙</v>
       </c>
     </row>
-    <row r="350" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="350" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A350" s="15" t="s">
         <v>2460</v>
       </c>
@@ -44770,7 +44842,7 @@
         <v>彭逃华</v>
       </c>
     </row>
-    <row r="351" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="351" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A351" s="15" t="s">
         <v>2465</v>
       </c>
@@ -44818,7 +44890,7 @@
         <v>刘佳 宋勇晖</v>
       </c>
     </row>
-    <row r="352" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="352" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A352" s="15" t="s">
         <v>2472</v>
       </c>
@@ -44866,7 +44938,7 @@
         <v>刘军平 郭小梅</v>
       </c>
     </row>
-    <row r="353" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="353" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A353" s="15" t="s">
         <v>2479</v>
       </c>
@@ -44908,7 +44980,7 @@
         <v>吴弘</v>
       </c>
     </row>
-    <row r="354" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="354" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A354" s="15" t="s">
         <v>2484</v>
       </c>
@@ -44956,7 +45028,7 @@
         <v>郭惠钧 刘婷婷</v>
       </c>
     </row>
-    <row r="355" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="355" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A355" s="15" t="s">
         <v>2491</v>
       </c>
@@ -45004,7 +45076,7 @@
         <v>曾德志 朱淑芳</v>
       </c>
     </row>
-    <row r="356" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="356" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A356" s="15" t="s">
         <v>2498</v>
       </c>
@@ -45046,7 +45118,7 @@
         <v/>
       </c>
     </row>
-    <row r="357" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A357" s="15" t="s">
         <v>2504</v>
       </c>
@@ -45092,7 +45164,7 @@
         <v>卢忠星 吴丹</v>
       </c>
     </row>
-    <row r="358" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A358" s="15" t="s">
         <v>2511</v>
       </c>
@@ -45130,7 +45202,7 @@
         <v/>
       </c>
     </row>
-    <row r="359" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="359" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A359" s="15" t="s">
         <v>2517</v>
       </c>
@@ -45178,7 +45250,7 @@
         <v>曾小卿 袁维娟</v>
       </c>
     </row>
-    <row r="360" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A360" s="15" t="s">
         <v>2524</v>
       </c>
@@ -45214,7 +45286,7 @@
         <v/>
       </c>
     </row>
-    <row r="361" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="361" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A361" s="15" t="s">
         <v>2528</v>
       </c>
@@ -45250,7 +45322,7 @@
         <v/>
       </c>
     </row>
-    <row r="362" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A362" s="15" t="s">
         <v>2532</v>
       </c>
@@ -45286,7 +45358,7 @@
         <v/>
       </c>
     </row>
-    <row r="363" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A363" s="15" t="s">
         <v>2536</v>
       </c>
@@ -45326,7 +45398,7 @@
         <v/>
       </c>
     </row>
-    <row r="364" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A364" s="15" t="s">
         <v>2542</v>
       </c>
@@ -45366,7 +45438,7 @@
         <v/>
       </c>
     </row>
-    <row r="365" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A365" s="15" t="s">
         <v>2548</v>
       </c>
@@ -45526,7 +45598,7 @@
         <v>郭文</v>
       </c>
     </row>
-    <row r="369" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A369" s="15" t="s">
         <v>2569</v>
       </c>
@@ -45566,7 +45638,7 @@
         <v>徐建国</v>
       </c>
     </row>
-    <row r="370" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="370" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A370" s="15" t="s">
         <v>2574</v>
       </c>
@@ -45610,7 +45682,7 @@
         <v>李衡 李蓉</v>
       </c>
     </row>
-    <row r="371" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="371" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A371" s="15" t="s">
         <v>2581</v>
       </c>
@@ -45698,7 +45770,7 @@
         <v>张艳 徐礼文</v>
       </c>
     </row>
-    <row r="373" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="373" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A373" s="15" t="s">
         <v>2595</v>
       </c>
@@ -45740,7 +45812,7 @@
         <v>彭杰</v>
       </c>
     </row>
-    <row r="374" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="374" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A374" s="15" t="s">
         <v>2600</v>
       </c>
@@ -45776,7 +45848,7 @@
         <v/>
       </c>
     </row>
-    <row r="375" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="375" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A375" s="15" t="s">
         <v>2604</v>
       </c>
@@ -45824,7 +45896,7 @@
         <v>张硕 彭韶琴</v>
       </c>
     </row>
-    <row r="376" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="376" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A376" s="15" t="s">
         <v>2611</v>
       </c>
@@ -45872,7 +45944,7 @@
         <v>钟春光 肖春华</v>
       </c>
     </row>
-    <row r="377" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A377" s="15" t="s">
         <v>2618</v>
       </c>
@@ -45918,7 +45990,7 @@
         <v>刘先代 刘丽琴</v>
       </c>
     </row>
-    <row r="378" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A378" s="15" t="s">
         <v>2621</v>
       </c>
@@ -45964,7 +46036,7 @@
         <v>刘先代 刘丽琴</v>
       </c>
     </row>
-    <row r="379" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A379" s="15" t="s">
         <v>2623</v>
       </c>
@@ -46004,7 +46076,7 @@
         <v/>
       </c>
     </row>
-    <row r="380" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="380" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A380" s="15" t="s">
         <v>2630</v>
       </c>
@@ -46040,7 +46112,7 @@
         <v/>
       </c>
     </row>
-    <row r="381" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="381" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A381" s="15" t="s">
         <v>2634</v>
       </c>
@@ -46080,7 +46152,7 @@
         <v/>
       </c>
     </row>
-    <row r="382" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A382" s="15" t="s">
         <v>2641</v>
       </c>
@@ -46126,7 +46198,7 @@
         <v>马玉娇 江海</v>
       </c>
     </row>
-    <row r="383" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A383" s="15" t="s">
         <v>2644</v>
       </c>
@@ -46172,7 +46244,7 @@
         <v>王婷 廖智茂</v>
       </c>
     </row>
-    <row r="384" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A384" s="15" t="s">
         <v>2651</v>
       </c>
@@ -46218,7 +46290,7 @@
         <v>王婷 廖智茂</v>
       </c>
     </row>
-    <row r="385" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="385" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A385" s="15" t="s">
         <v>2653</v>
       </c>
@@ -46260,7 +46332,7 @@
         <v>王清云</v>
       </c>
     </row>
-    <row r="386" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="386" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A386" s="15" t="s">
         <v>2659</v>
       </c>
@@ -46308,7 +46380,7 @@
         <v>高林 刘敏</v>
       </c>
     </row>
-    <row r="387" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="387" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A387" s="15" t="s">
         <v>2668</v>
       </c>
@@ -46350,7 +46422,7 @@
         <v>郭臧怡</v>
       </c>
     </row>
-    <row r="388" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="388" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A388" s="15" t="s">
         <v>2674</v>
       </c>
@@ -46398,7 +46470,7 @@
         <v>曾安琪 孙天黎</v>
       </c>
     </row>
-    <row r="389" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="389" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A389" s="15" t="s">
         <v>2683</v>
       </c>
@@ -46438,7 +46510,7 @@
         <v/>
       </c>
     </row>
-    <row r="390" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="390" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A390" s="15" t="s">
         <v>2690</v>
       </c>
@@ -46478,7 +46550,7 @@
         <v/>
       </c>
     </row>
-    <row r="391" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="391" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A391" s="15" t="s">
         <v>2697</v>
       </c>
@@ -46518,7 +46590,7 @@
         <v/>
       </c>
     </row>
-    <row r="392" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="392" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A392" s="15" t="s">
         <v>2703</v>
       </c>
@@ -46566,7 +46638,7 @@
         <v>刘智龙 胡佳</v>
       </c>
     </row>
-    <row r="393" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="393" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A393" s="15" t="s">
         <v>2713</v>
       </c>
@@ -46612,7 +46684,7 @@
         <v>李仁华 吴小琴</v>
       </c>
     </row>
-    <row r="394" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="394" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A394" s="15" t="s">
         <v>2721</v>
       </c>
@@ -46660,7 +46732,7 @@
         <v>彭新风 刘辉</v>
       </c>
     </row>
-    <row r="395" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="395" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A395" s="15" t="s">
         <v>2724</v>
       </c>
@@ -46702,7 +46774,7 @@
         <v>谢吉翔</v>
       </c>
     </row>
-    <row r="396" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="396" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A396" s="15" t="s">
         <v>2730</v>
       </c>
@@ -46744,7 +46816,7 @@
         <v>周水元</v>
       </c>
     </row>
-    <row r="397" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="397" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A397" s="15" t="s">
         <v>2736</v>
       </c>
@@ -46786,7 +46858,7 @@
         <v>冷小婷</v>
       </c>
     </row>
-    <row r="398" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A398" s="15" t="s">
         <v>2742</v>
       </c>
@@ -46828,7 +46900,7 @@
         <v>李梅英</v>
       </c>
     </row>
-    <row r="399" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="399" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A399" s="15" t="s">
         <v>2748</v>
       </c>
@@ -46874,7 +46946,7 @@
         <v>罗招凤 刘涛</v>
       </c>
     </row>
-    <row r="400" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="400" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A400" s="15" t="s">
         <v>2756</v>
       </c>
@@ -46910,7 +46982,7 @@
         <v/>
       </c>
     </row>
-    <row r="401" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="401" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A401" s="15" t="s">
         <v>2761</v>
       </c>
@@ -46950,7 +47022,7 @@
         <v/>
       </c>
     </row>
-    <row r="402" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="402" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A402" s="15" t="s">
         <v>2768</v>
       </c>
@@ -46992,7 +47064,7 @@
         <v>李洪彬</v>
       </c>
     </row>
-    <row r="403" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="403" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A403" s="15" t="s">
         <v>2774</v>
       </c>
@@ -47040,7 +47112,7 @@
         <v>杨陈朱 黄强</v>
       </c>
     </row>
-    <row r="404" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A404" s="15" t="s">
         <v>2783</v>
       </c>
@@ -47082,7 +47154,7 @@
         <v>邹兰青</v>
       </c>
     </row>
-    <row r="405" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="405" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A405" s="15" t="s">
         <v>2785</v>
       </c>
@@ -47124,7 +47196,7 @@
         <v>刘金龙</v>
       </c>
     </row>
-    <row r="406" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="406" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A406" s="15" t="s">
         <v>2791</v>
       </c>
@@ -47170,7 +47242,7 @@
         <v>张欣 张丽花</v>
       </c>
     </row>
-    <row r="407" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="407" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A407" s="15" t="s">
         <v>2799</v>
       </c>
@@ -47218,7 +47290,7 @@
         <v>刘天学 罗芳</v>
       </c>
     </row>
-    <row r="408" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="408" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A408" s="15" t="s">
         <v>2808</v>
       </c>
@@ -47266,7 +47338,7 @@
         <v>罗英英 曾国慧</v>
       </c>
     </row>
-    <row r="409" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="409" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A409" s="15" t="s">
         <v>2817</v>
       </c>
@@ -47306,7 +47378,7 @@
         <v/>
       </c>
     </row>
-    <row r="410" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="410" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A410" s="15" t="s">
         <v>2824</v>
       </c>
@@ -47346,7 +47418,7 @@
         <v/>
       </c>
     </row>
-    <row r="411" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="411" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A411" s="15" t="s">
         <v>2831</v>
       </c>
@@ -47386,7 +47458,7 @@
         <v/>
       </c>
     </row>
-    <row r="412" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="412" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A412" s="15" t="s">
         <v>2838</v>
       </c>
@@ -47422,7 +47494,7 @@
         <v/>
       </c>
     </row>
-    <row r="413" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A413" s="15" t="s">
         <v>2843</v>
       </c>
@@ -47470,7 +47542,7 @@
         <v>许晓丽 郭力勇</v>
       </c>
     </row>
-    <row r="414" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="414" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A414" s="15" t="s">
         <v>2848</v>
       </c>
@@ -47518,7 +47590,7 @@
         <v>许晓丽 郭力勇</v>
       </c>
     </row>
-    <row r="415" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="415" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A415" s="15" t="s">
         <v>2850</v>
       </c>
@@ -47560,7 +47632,7 @@
         <v>钟婷</v>
       </c>
     </row>
-    <row r="416" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="416" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A416" s="15" t="s">
         <v>2856</v>
       </c>
@@ -47602,7 +47674,7 @@
         <v>黄扬</v>
       </c>
     </row>
-    <row r="417" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="417" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A417" s="15" t="s">
         <v>2862</v>
       </c>
@@ -47650,7 +47722,7 @@
         <v>周玥 周俊浩</v>
       </c>
     </row>
-    <row r="418" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="418" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A418" s="15" t="s">
         <v>2871</v>
       </c>
@@ -47690,7 +47762,7 @@
         <v/>
       </c>
     </row>
-    <row r="419" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="419" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A419" s="15" t="s">
         <v>2878</v>
       </c>
@@ -47730,7 +47802,7 @@
         <v/>
       </c>
     </row>
-    <row r="420" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="420" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A420" s="15" t="s">
         <v>2885</v>
       </c>
@@ -47770,7 +47842,7 @@
         <v/>
       </c>
     </row>
-    <row r="421" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="421" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A421" s="15" t="s">
         <v>2892</v>
       </c>
@@ -47810,7 +47882,7 @@
         <v/>
       </c>
     </row>
-    <row r="422" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="422" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A422" s="15" t="s">
         <v>2899</v>
       </c>
@@ -47858,7 +47930,7 @@
         <v>刘智新 汪爱华</v>
       </c>
     </row>
-    <row r="423" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="423" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A423" s="15" t="s">
         <v>2903</v>
       </c>
@@ -47898,7 +47970,7 @@
         <v/>
       </c>
     </row>
-    <row r="424" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="424" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A424" s="15" t="s">
         <v>2910</v>
       </c>
@@ -47944,7 +48016,7 @@
         <v>黄学考 林仙燕</v>
       </c>
     </row>
-    <row r="425" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="425" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A425" s="15" t="s">
         <v>2913</v>
       </c>
@@ -47990,7 +48062,7 @@
         <v>黄学考 林仙燕</v>
       </c>
     </row>
-    <row r="426" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="426" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A426" s="15" t="s">
         <v>2915</v>
       </c>
@@ -48036,7 +48108,7 @@
         <v>吴宫兰 龙小卫</v>
       </c>
     </row>
-    <row r="427" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="427" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A427" s="15" t="s">
         <v>2923</v>
       </c>
@@ -48078,7 +48150,7 @@
         <v>吴倩倩</v>
       </c>
     </row>
-    <row r="428" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="428" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A428" s="15" t="s">
         <v>2929</v>
       </c>
@@ -48120,7 +48192,7 @@
         <v>胡慧婷</v>
       </c>
     </row>
-    <row r="429" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="429" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A429" s="15" t="s">
         <v>2935</v>
       </c>
@@ -48160,7 +48232,7 @@
         <v/>
       </c>
     </row>
-    <row r="430" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="430" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A430" s="15" t="s">
         <v>2942</v>
       </c>
@@ -48202,7 +48274,7 @@
         <v>周忠民</v>
       </c>
     </row>
-    <row r="431" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="431" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A431" s="15" t="s">
         <v>2948</v>
       </c>
@@ -48250,7 +48322,7 @@
         <v>郭朝东 邱峻</v>
       </c>
     </row>
-    <row r="432" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="432" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A432" s="15" t="s">
         <v>2957</v>
       </c>
@@ -48296,7 +48368,7 @@
         <v>喻智勇 梁珍兰</v>
       </c>
     </row>
-    <row r="433" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="433" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A433" s="15" t="s">
         <v>2959</v>
       </c>
@@ -48336,7 +48408,7 @@
         <v/>
       </c>
     </row>
-    <row r="434" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="434" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A434" s="15" t="s">
         <v>2965</v>
       </c>
@@ -48376,7 +48448,7 @@
         <v/>
       </c>
     </row>
-    <row r="435" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="435" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A435" s="15" t="s">
         <v>2972</v>
       </c>
@@ -48418,7 +48490,7 @@
         <v>刘华清</v>
       </c>
     </row>
-    <row r="436" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="436" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A436" s="15" t="s">
         <v>2978</v>
       </c>
@@ -48460,7 +48532,7 @@
         <v>刘华清</v>
       </c>
     </row>
-    <row r="437" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="437" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A437" s="15" t="s">
         <v>2980</v>
       </c>
@@ -48500,7 +48572,7 @@
         <v/>
       </c>
     </row>
-    <row r="438" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="438" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438" s="15" t="s">
         <v>2987</v>
       </c>
@@ -48540,7 +48612,7 @@
         <v/>
       </c>
     </row>
-    <row r="439" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="439" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A439" s="15" t="s">
         <v>2994</v>
       </c>
@@ -48576,7 +48648,7 @@
         <v/>
       </c>
     </row>
-    <row r="440" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="440" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A440" s="15" t="s">
         <v>2995</v>
       </c>
@@ -48616,7 +48688,7 @@
         <v/>
       </c>
     </row>
-    <row r="441" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="441" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A441" s="15" t="s">
         <v>3002</v>
       </c>
@@ -48658,7 +48730,7 @@
         <v>王辉华</v>
       </c>
     </row>
-    <row r="442" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="442" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A442" s="15" t="s">
         <v>3008</v>
       </c>
@@ -48700,7 +48772,7 @@
         <v>朱小花</v>
       </c>
     </row>
-    <row r="443" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="443" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A443" s="15" t="s">
         <v>3014</v>
       </c>
@@ -48748,7 +48820,7 @@
         <v>王海龙 施丹丹</v>
       </c>
     </row>
-    <row r="444" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="444" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A444" s="15" t="s">
         <v>3023</v>
       </c>
@@ -48790,7 +48862,7 @@
         <v>丁琴英</v>
       </c>
     </row>
-    <row r="445" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="445" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A445" s="15" t="s">
         <v>3029</v>
       </c>
@@ -48832,7 +48904,7 @@
         <v>丁琴英</v>
       </c>
     </row>
-    <row r="446" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="446" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A446" s="15" t="s">
         <v>3031</v>
       </c>
@@ -48866,7 +48938,7 @@
         <v/>
       </c>
     </row>
-    <row r="447" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="447" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A447" s="15" t="s">
         <v>3033</v>
       </c>
@@ -48906,7 +48978,7 @@
         <v/>
       </c>
     </row>
-    <row r="448" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="448" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A448" s="15" t="s">
         <v>3040</v>
       </c>
@@ -48948,7 +49020,7 @@
         <v>罗敬财</v>
       </c>
     </row>
-    <row r="449" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="449" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A449" s="15" t="s">
         <v>3046</v>
       </c>
@@ -48984,7 +49056,7 @@
         <v/>
       </c>
     </row>
-    <row r="450" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="450" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A450" s="15" t="s">
         <v>3051</v>
       </c>
@@ -49024,7 +49096,7 @@
         <v/>
       </c>
     </row>
-    <row r="451" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="451" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A451" s="15" t="s">
         <v>3058</v>
       </c>
@@ -49066,7 +49138,7 @@
         <v>殷梅林</v>
       </c>
     </row>
-    <row r="452" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="452" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A452" s="15" t="s">
         <v>3064</v>
       </c>
@@ -49108,7 +49180,7 @@
         <v>肖静文</v>
       </c>
     </row>
-    <row r="453" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="453" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A453" s="15" t="s">
         <v>3070</v>
       </c>
@@ -49150,7 +49222,7 @@
         <v>张呈香</v>
       </c>
     </row>
-    <row r="454" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="454" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A454" s="15" t="s">
         <v>3076</v>
       </c>
@@ -49192,7 +49264,7 @@
         <v>王志民</v>
       </c>
     </row>
-    <row r="455" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="455" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A455" s="15" t="s">
         <v>3082</v>
       </c>
@@ -49226,7 +49298,7 @@
         <v/>
       </c>
     </row>
-    <row r="456" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="456" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A456" s="15" t="s">
         <v>3086</v>
       </c>
@@ -49262,7 +49334,7 @@
         <v/>
       </c>
     </row>
-    <row r="457" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="457" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A457" s="15" t="s">
         <v>3091</v>
       </c>
@@ -49300,7 +49372,7 @@
         <v/>
       </c>
     </row>
-    <row r="458" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="458" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A458" s="15" t="s">
         <v>3097</v>
       </c>
@@ -49336,7 +49408,7 @@
         <v/>
       </c>
     </row>
-    <row r="459" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="459" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A459" s="15" t="s">
         <v>3102</v>
       </c>
@@ -49374,7 +49446,7 @@
         <v/>
       </c>
     </row>
-    <row r="460" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="460" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A460" s="15" t="s">
         <v>3108</v>
       </c>
@@ -49410,7 +49482,7 @@
         <v/>
       </c>
     </row>
-    <row r="461" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="461" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A461" s="15" t="s">
         <v>3113</v>
       </c>
@@ -49450,7 +49522,7 @@
         <v/>
       </c>
     </row>
-    <row r="462" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="462" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A462" s="15" t="s">
         <v>3116</v>
       </c>
@@ -49488,7 +49560,7 @@
         <v/>
       </c>
     </row>
-    <row r="463" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="463" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A463" s="15" t="s">
         <v>3122</v>
       </c>
@@ -49526,7 +49598,7 @@
         <v/>
       </c>
     </row>
-    <row r="464" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="464" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A464" s="15" t="s">
         <v>3128</v>
       </c>
@@ -49564,7 +49636,7 @@
         <v/>
       </c>
     </row>
-    <row r="465" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="465" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A465" s="15" t="s">
         <v>3134</v>
       </c>
@@ -49608,7 +49680,7 @@
         <v/>
       </c>
     </row>
-    <row r="466" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="466" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466" s="15" t="s">
         <v>3135</v>
       </c>
@@ -49642,7 +49714,7 @@
         <v/>
       </c>
     </row>
-    <row r="467" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="467" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A467" s="15" t="s">
         <v>3139</v>
       </c>
@@ -49684,7 +49756,7 @@
         <v>彭重扬</v>
       </c>
     </row>
-    <row r="468" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="468" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A468" s="15" t="s">
         <v>3145</v>
       </c>
@@ -49718,7 +49790,7 @@
         <v/>
       </c>
     </row>
-    <row r="469" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="469" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A469" s="15" t="s">
         <v>3146</v>
       </c>
@@ -49760,7 +49832,7 @@
         <v>邓盼</v>
       </c>
     </row>
-    <row r="470" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="470" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A470" s="15" t="s">
         <v>3152</v>
       </c>
@@ -49802,7 +49874,7 @@
         <v>钟青兰</v>
       </c>
     </row>
-    <row r="471" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="471" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A471" s="15" t="s">
         <v>3158</v>
       </c>
@@ -49848,7 +49920,7 @@
         <v>王喜民 王小燕</v>
       </c>
     </row>
-    <row r="472" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="472" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A472" s="15" t="s">
         <v>3161</v>
       </c>
@@ -49894,7 +49966,7 @@
         <v>李伍毛 邹红英</v>
       </c>
     </row>
-    <row r="473" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="473" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A473" s="15" t="s">
         <v>3169</v>
       </c>
@@ -49934,7 +50006,7 @@
         <v/>
       </c>
     </row>
-    <row r="474" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="474" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A474" s="15" t="s">
         <v>3176</v>
       </c>
@@ -49972,7 +50044,7 @@
         <v/>
       </c>
     </row>
-    <row r="475" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="475" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A475" s="15" t="s">
         <v>3182</v>
       </c>
@@ -50010,7 +50082,7 @@
         <v/>
       </c>
     </row>
-    <row r="476" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="476" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A476" s="15" t="s">
         <v>3188</v>
       </c>
@@ -50050,7 +50122,7 @@
         <v/>
       </c>
     </row>
-    <row r="477" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="477" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A477" s="15" t="s">
         <v>3195</v>
       </c>
@@ -50090,7 +50162,7 @@
         <v/>
       </c>
     </row>
-    <row r="478" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="478" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A478" s="15" t="s">
         <v>3202</v>
       </c>
@@ -50130,7 +50202,7 @@
         <v/>
       </c>
     </row>
-    <row r="479" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="479" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A479" s="15" t="s">
         <v>3209</v>
       </c>
@@ -50170,7 +50242,7 @@
         <v/>
       </c>
     </row>
-    <row r="480" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="480" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A480" s="15" t="s">
         <v>3216</v>
       </c>
@@ -50208,7 +50280,7 @@
         <v/>
       </c>
     </row>
-    <row r="481" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="481" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A481" s="15" t="s">
         <v>3222</v>
       </c>
@@ -50250,7 +50322,7 @@
         <v>盛德豪</v>
       </c>
     </row>
-    <row r="482" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="482" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A482" s="15" t="s">
         <v>3228</v>
       </c>
@@ -50292,7 +50364,7 @@
         <v>盛德豪</v>
       </c>
     </row>
-    <row r="483" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="483" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A483" s="15" t="s">
         <v>3230</v>
       </c>
@@ -50338,7 +50410,7 @@
         <v>邓高生 严小英</v>
       </c>
     </row>
-    <row r="484" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="484" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A484" s="15" t="s">
         <v>3238</v>
       </c>
@@ -50386,7 +50458,7 @@
         <v>宋光太 匡秀华</v>
       </c>
     </row>
-    <row r="485" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="485" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A485" s="15" t="s">
         <v>3247</v>
       </c>
@@ -50432,7 +50504,7 @@
         <v>杨晓锐 黄建华</v>
       </c>
     </row>
-    <row r="486" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="486" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A486" s="15" t="s">
         <v>3255</v>
       </c>
@@ -50474,7 +50546,7 @@
         <v>宋文佳</v>
       </c>
     </row>
-    <row r="487" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="487" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A487" s="15" t="s">
         <v>3261</v>
       </c>
@@ -50514,7 +50586,7 @@
         <v/>
       </c>
     </row>
-    <row r="488" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="488" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A488" s="15" t="s">
         <v>3268</v>
       </c>
@@ -50556,7 +50628,7 @@
         <v>李树光</v>
       </c>
     </row>
-    <row r="489" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="489" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A489" s="15" t="s">
         <v>3272</v>
       </c>
@@ -50602,7 +50674,7 @@
         <v>毛年香 王明强</v>
       </c>
     </row>
-    <row r="490" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="490" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A490" s="15" t="s">
         <v>3275</v>
       </c>
@@ -50642,7 +50714,7 @@
         <v/>
       </c>
     </row>
-    <row r="491" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="491" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A491" s="15" t="s">
         <v>3282</v>
       </c>
@@ -50682,7 +50754,7 @@
         <v/>
       </c>
     </row>
-    <row r="492" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="492" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A492" s="15" t="s">
         <v>3289</v>
       </c>
@@ -50720,7 +50792,7 @@
         <v/>
       </c>
     </row>
-    <row r="493" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="493" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A493" s="15" t="s">
         <v>3295</v>
       </c>
@@ -50760,7 +50832,7 @@
         <v/>
       </c>
     </row>
-    <row r="494" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="494" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A494" s="15" t="s">
         <v>3302</v>
       </c>
@@ -50796,7 +50868,7 @@
         <v/>
       </c>
     </row>
-    <row r="495" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="495" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A495" s="15" t="s">
         <v>3307</v>
       </c>
@@ -50836,7 +50908,7 @@
         <v/>
       </c>
     </row>
-    <row r="496" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="496" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A496" s="15" t="s">
         <v>3314</v>
       </c>
@@ -50878,7 +50950,7 @@
         <v/>
       </c>
     </row>
-    <row r="497" spans="1:15" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="497" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A497" s="15" t="s">
         <v>3321</v>
       </c>
@@ -50915,7 +50987,7 @@
         <v/>
       </c>
     </row>
-    <row r="498" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="498" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A498" s="15" t="s">
         <v>3327</v>
       </c>
@@ -50955,7 +51027,7 @@
         <v/>
       </c>
     </row>
-    <row r="499" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="499" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A499" s="15" t="s">
         <v>3334</v>
       </c>
@@ -50991,7 +51063,7 @@
         <v/>
       </c>
     </row>
-    <row r="500" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="500" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A500" s="15" t="s">
         <v>3339</v>
       </c>
@@ -51031,7 +51103,7 @@
         <v/>
       </c>
     </row>
-    <row r="501" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="501" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A501" s="15" t="s">
         <v>3346</v>
       </c>
@@ -51067,7 +51139,7 @@
         <v/>
       </c>
     </row>
-    <row r="502" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="502" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A502" s="15" t="s">
         <v>3351</v>
       </c>
@@ -51107,7 +51179,7 @@
         <v/>
       </c>
     </row>
-    <row r="503" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="503" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A503" s="15" t="s">
         <v>3358</v>
       </c>
@@ -51149,7 +51221,7 @@
         <v>王小慧</v>
       </c>
     </row>
-    <row r="504" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
+    <row r="504" spans="1:15" ht="54" x14ac:dyDescent="0.15">
       <c r="A504" s="15" t="s">
         <v>3364</v>
       </c>
@@ -51241,7 +51313,7 @@
         <v>刘镇平 彭满娇</v>
       </c>
     </row>
-    <row r="506" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="506" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A506" s="15" t="s">
         <v>3374</v>
       </c>
@@ -51285,7 +51357,7 @@
         <v>戴林军 陈素贞</v>
       </c>
     </row>
-    <row r="507" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="507" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A507" s="15" t="s">
         <v>3382</v>
       </c>
@@ -51325,7 +51397,7 @@
         <v>李锋明</v>
       </c>
     </row>
-    <row r="508" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="508" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A508" s="15" t="s">
         <v>3388</v>
       </c>
@@ -51367,7 +51439,7 @@
         <v>文雯</v>
       </c>
     </row>
-    <row r="509" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="509" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A509" s="15" t="s">
         <v>3394</v>
       </c>
@@ -51409,7 +51481,7 @@
         <v>朱雪莲</v>
       </c>
     </row>
-    <row r="510" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="510" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A510" s="15" t="s">
         <v>3400</v>
       </c>
@@ -51455,7 +51527,7 @@
         <v>张细苟 谭春莲</v>
       </c>
     </row>
-    <row r="511" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="511" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A511" s="15" t="s">
         <v>3408</v>
       </c>
@@ -51503,7 +51575,7 @@
         <v>郭芳金 卢芳兰</v>
       </c>
     </row>
-    <row r="512" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="512" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A512" s="15" t="s">
         <v>3417</v>
       </c>
@@ -51543,7 +51615,7 @@
         <v/>
       </c>
     </row>
-    <row r="513" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="513" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A513" s="15" t="s">
         <v>3424</v>
       </c>
@@ -51583,7 +51655,7 @@
         <v/>
       </c>
     </row>
-    <row r="514" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="514" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A514" s="15" t="s">
         <v>3431</v>
       </c>
@@ -51623,7 +51695,7 @@
         <v/>
       </c>
     </row>
-    <row r="515" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="515" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A515" s="15" t="s">
         <v>3438</v>
       </c>
@@ -51659,7 +51731,7 @@
         <v/>
       </c>
     </row>
-    <row r="516" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="516" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A516" s="15" t="s">
         <v>3443</v>
       </c>
@@ -51695,7 +51767,7 @@
         <v/>
       </c>
     </row>
-    <row r="517" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="517" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A517" s="15" t="s">
         <v>3448</v>
       </c>
@@ -51735,7 +51807,7 @@
         <v/>
       </c>
     </row>
-    <row r="518" spans="1:15" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="518" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A518" s="15" t="s">
         <v>3455</v>
       </c>
@@ -51771,7 +51843,7 @@
         <v/>
       </c>
     </row>
-    <row r="519" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="519" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A519" s="15" t="s">
         <v>3460</v>
       </c>
@@ -51819,7 +51891,7 @@
         <v>宋文斌 肖丽</v>
       </c>
     </row>
-    <row r="520" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="520" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A520" s="15" t="s">
         <v>3469</v>
       </c>
@@ -51861,7 +51933,7 @@
         <v>郭贞云</v>
       </c>
     </row>
-    <row r="521" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="521" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A521" s="15" t="s">
         <v>3475</v>
       </c>
@@ -51909,7 +51981,7 @@
         <v>李娟 胡昊</v>
       </c>
     </row>
-    <row r="522" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="522" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A522" s="15" t="s">
         <v>3484</v>
       </c>
@@ -51955,7 +52027,7 @@
         <v>李娜 肖诗靓</v>
       </c>
     </row>
-    <row r="523" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="523" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A523" s="15" t="s">
         <v>3492</v>
       </c>
@@ -52003,7 +52075,7 @@
         <v>周学勤 邓俊超</v>
       </c>
     </row>
-    <row r="524" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="524" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A524" s="15" t="s">
         <v>3501</v>
       </c>
@@ -52039,7 +52111,7 @@
         <v/>
       </c>
     </row>
-    <row r="525" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="525" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A525" s="15" t="s">
         <v>3506</v>
       </c>
@@ -52081,7 +52153,7 @@
         <v/>
       </c>
     </row>
-    <row r="526" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
+    <row r="526" spans="1:15" ht="54" x14ac:dyDescent="0.15">
       <c r="A526" s="15" t="s">
         <v>3514</v>
       </c>
@@ -52127,7 +52199,7 @@
         <v>黄钟龙 李娟红</v>
       </c>
     </row>
-    <row r="527" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="527" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A527" s="15" t="s">
         <v>3522</v>
       </c>
@@ -52175,7 +52247,7 @@
         <v>田鹏显 雷莲芳</v>
       </c>
     </row>
-    <row r="528" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="528" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A528" s="15" t="s">
         <v>3531</v>
       </c>
@@ -52223,7 +52295,7 @@
         <v>廖声兵 谢金香</v>
       </c>
     </row>
-    <row r="529" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="529" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A529" s="15" t="s">
         <v>3540</v>
       </c>
@@ -52265,7 +52337,7 @@
         <v>杨成浪</v>
       </c>
     </row>
-    <row r="530" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="530" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A530" s="15" t="s">
         <v>3546</v>
       </c>
@@ -52299,7 +52371,7 @@
         <v/>
       </c>
     </row>
-    <row r="531" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="531" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A531" s="15" t="s">
         <v>3550</v>
       </c>
@@ -52333,7 +52405,7 @@
         <v/>
       </c>
     </row>
-    <row r="532" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="532" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A532" s="15" t="s">
         <v>3554</v>
       </c>
@@ -52367,7 +52439,7 @@
         <v/>
       </c>
     </row>
-    <row r="533" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="533" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A533" s="15" t="s">
         <v>3558</v>
       </c>
@@ -52405,7 +52477,7 @@
         <v/>
       </c>
     </row>
-    <row r="534" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="534" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A534" s="15" t="s">
         <v>3564</v>
       </c>
@@ -52443,7 +52515,7 @@
         <v/>
       </c>
     </row>
-    <row r="535" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="535" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A535" s="15" t="s">
         <v>3570</v>
       </c>
@@ -52481,7 +52553,7 @@
         <v/>
       </c>
     </row>
-    <row r="536" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="536" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A536" s="15" t="s">
         <v>3576</v>
       </c>
@@ -52519,7 +52591,7 @@
         <v/>
       </c>
     </row>
-    <row r="537" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="537" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A537" s="15" t="s">
         <v>3582</v>
       </c>
@@ -52557,7 +52629,7 @@
         <v/>
       </c>
     </row>
-    <row r="538" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="538" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A538" s="15" t="s">
         <v>3588</v>
       </c>
@@ -52605,7 +52677,7 @@
         <v>肖文婧 吴德强</v>
       </c>
     </row>
-    <row r="539" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="539" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A539" s="15" t="s">
         <v>3597</v>
       </c>
@@ -52653,7 +52725,7 @@
         <v>郭婷 曾纪帅</v>
       </c>
     </row>
-    <row r="540" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="540" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A540" s="15" t="s">
         <v>3606</v>
       </c>
@@ -52701,7 +52773,7 @@
         <v>古桂兰 赖文祥</v>
       </c>
     </row>
-    <row r="541" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="541" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A541" s="15" t="s">
         <v>3615</v>
       </c>
@@ -52747,7 +52819,7 @@
         <v>肖兰平 胡苏平</v>
       </c>
     </row>
-    <row r="542" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="542" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A542" s="15" t="s">
         <v>3623</v>
       </c>
@@ -52783,7 +52855,7 @@
         <v/>
       </c>
     </row>
-    <row r="543" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="543" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A543" s="15" t="s">
         <v>3628</v>
       </c>
@@ -52829,7 +52901,7 @@
         <v>高惠明 刘诗华</v>
       </c>
     </row>
-    <row r="544" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="544" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A544" s="15" t="s">
         <v>3636</v>
       </c>
@@ -52877,7 +52949,7 @@
         <v>郭玉令 陈小燕</v>
       </c>
     </row>
-    <row r="545" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="545" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A545" s="15" t="s">
         <v>3645</v>
       </c>
@@ -52919,7 +52991,7 @@
         <v>吉安市永宾商贸有限公司</v>
       </c>
     </row>
-    <row r="546" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="546" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A546" s="15" t="s">
         <v>3651</v>
       </c>
@@ -52953,7 +53025,7 @@
         <v/>
       </c>
     </row>
-    <row r="547" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="547" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A547" s="15" t="s">
         <v>3655</v>
       </c>
@@ -52991,7 +53063,7 @@
         <v/>
       </c>
     </row>
-    <row r="548" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="548" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A548" s="15" t="s">
         <v>3661</v>
       </c>
@@ -53029,7 +53101,7 @@
         <v/>
       </c>
     </row>
-    <row r="549" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="549" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A549" s="15" t="s">
         <v>3667</v>
       </c>
@@ -53065,7 +53137,7 @@
         <v/>
       </c>
     </row>
-    <row r="550" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="550" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A550" s="15" t="s">
         <v>3672</v>
       </c>
@@ -53103,7 +53175,7 @@
         <v/>
       </c>
     </row>
-    <row r="551" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="551" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A551" s="15" t="s">
         <v>3678</v>
       </c>
@@ -53137,7 +53209,7 @@
         <v/>
       </c>
     </row>
-    <row r="552" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="552" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A552" s="15" t="s">
         <v>3682</v>
       </c>
@@ -53171,7 +53243,7 @@
         <v/>
       </c>
     </row>
-    <row r="553" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="553" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A553" s="15" t="s">
         <v>3686</v>
       </c>
@@ -53209,7 +53281,7 @@
         <v/>
       </c>
     </row>
-    <row r="554" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="554" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A554" s="15" t="s">
         <v>3692</v>
       </c>
@@ -53251,7 +53323,7 @@
         <v>李珍红</v>
       </c>
     </row>
-    <row r="555" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="555" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A555" s="15" t="s">
         <v>3698</v>
       </c>
@@ -53299,7 +53371,7 @@
         <v>向敏 李荣</v>
       </c>
     </row>
-    <row r="556" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="556" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A556" s="15" t="s">
         <v>3707</v>
       </c>
@@ -53337,7 +53409,7 @@
         <v/>
       </c>
     </row>
-    <row r="557" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="557" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A557" s="15" t="s">
         <v>3713</v>
       </c>
@@ -53385,7 +53457,7 @@
         <v>肖桂兰 林善华</v>
       </c>
     </row>
-    <row r="558" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="558" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A558" s="15" t="s">
         <v>3722</v>
       </c>
@@ -53423,7 +53495,7 @@
         <v/>
       </c>
     </row>
-    <row r="559" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="559" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A559" s="15" t="s">
         <v>3728</v>
       </c>
@@ -53471,7 +53543,7 @@
         <v>王红艳 刘利</v>
       </c>
     </row>
-    <row r="560" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="560" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A560" s="15" t="s">
         <v>3737</v>
       </c>
@@ -53505,7 +53577,7 @@
         <v/>
       </c>
     </row>
-    <row r="561" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="561" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A561" s="15" t="s">
         <v>3741</v>
       </c>
@@ -53551,7 +53623,7 @@
         <v>黄少英 肖向阳</v>
       </c>
     </row>
-    <row r="562" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="562" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A562" s="15" t="s">
         <v>3744</v>
       </c>
@@ -53593,7 +53665,7 @@
         <v>周小燕</v>
       </c>
     </row>
-    <row r="563" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="563" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A563" s="15" t="s">
         <v>3750</v>
       </c>
@@ -53635,7 +53707,7 @@
         <v>陈军梅</v>
       </c>
     </row>
-    <row r="564" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="564" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A564" s="15" t="s">
         <v>3756</v>
       </c>
@@ -53683,7 +53755,7 @@
         <v>况根秀 张伟东</v>
       </c>
     </row>
-    <row r="565" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="565" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A565" s="15" t="s">
         <v>3765</v>
       </c>
@@ -53725,7 +53797,7 @@
         <v>张文娟</v>
       </c>
     </row>
-    <row r="566" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="566" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A566" s="15" t="s">
         <v>3768</v>
       </c>
@@ -53767,7 +53839,7 @@
         <v>庄宝娟</v>
       </c>
     </row>
-    <row r="567" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="567" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A567" s="15" t="s">
         <v>3774</v>
       </c>
@@ -53801,7 +53873,7 @@
         <v/>
       </c>
     </row>
-    <row r="568" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="568" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A568" s="15" t="s">
         <v>3778</v>
       </c>
@@ -53839,7 +53911,7 @@
         <v/>
       </c>
     </row>
-    <row r="569" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="569" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A569" s="15" t="s">
         <v>3784</v>
       </c>
@@ -53877,7 +53949,7 @@
         <v/>
       </c>
     </row>
-    <row r="570" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="570" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A570" s="15" t="s">
         <v>3790</v>
       </c>
@@ -53911,7 +53983,7 @@
         <v/>
       </c>
     </row>
-    <row r="571" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="571" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A571" s="15" t="s">
         <v>3794</v>
       </c>
@@ -53945,7 +54017,7 @@
         <v/>
       </c>
     </row>
-    <row r="572" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="572" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A572" s="15" t="s">
         <v>3798</v>
       </c>
@@ -53983,7 +54055,7 @@
         <v/>
       </c>
     </row>
-    <row r="573" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="573" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A573" s="15" t="s">
         <v>3804</v>
       </c>
@@ -54021,7 +54093,7 @@
         <v/>
       </c>
     </row>
-    <row r="574" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="574" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A574" s="15" t="s">
         <v>3810</v>
       </c>
@@ -54057,7 +54129,7 @@
         <v/>
       </c>
     </row>
-    <row r="575" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="575" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A575" s="15" t="s">
         <v>3815</v>
       </c>
@@ -54229,7 +54301,7 @@
         <v>刘启为</v>
       </c>
     </row>
-    <row r="579" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="579" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A579" s="15" t="s">
         <v>3829</v>
       </c>
@@ -54261,7 +54333,7 @@
         <v/>
       </c>
     </row>
-    <row r="580" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="580" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A580" s="15" t="s">
         <v>3832</v>
       </c>
@@ -54297,7 +54369,7 @@
         <v/>
       </c>
     </row>
-    <row r="581" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="581" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A581" s="15" t="s">
         <v>3837</v>
       </c>
@@ -54331,7 +54403,7 @@
         <v/>
       </c>
     </row>
-    <row r="582" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="582" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A582" s="15" t="s">
         <v>3841</v>
       </c>
@@ -54365,7 +54437,7 @@
         <v/>
       </c>
     </row>
-    <row r="583" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="583" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A583" s="15" t="s">
         <v>3845</v>
       </c>
@@ -54403,7 +54475,7 @@
         <v/>
       </c>
     </row>
-    <row r="584" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="584" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A584" s="15" t="s">
         <v>3851</v>
       </c>
@@ -54441,7 +54513,7 @@
         <v/>
       </c>
     </row>
-    <row r="585" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="585" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A585" s="15" t="s">
         <v>3857</v>
       </c>
@@ -54489,7 +54561,7 @@
         <v>刘韬 朱超</v>
       </c>
     </row>
-    <row r="586" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="586" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A586" s="15" t="s">
         <v>3866</v>
       </c>
@@ -54531,7 +54603,7 @@
         <v>邹龙滔</v>
       </c>
     </row>
-    <row r="587" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="587" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A587" s="15" t="s">
         <v>3872</v>
       </c>
@@ -54577,7 +54649,7 @@
         <v>叶师军 孙小琴</v>
       </c>
     </row>
-    <row r="588" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="588" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A588" s="15" t="s">
         <v>3880</v>
       </c>
@@ -54619,7 +54691,7 @@
         <v>黎舟</v>
       </c>
     </row>
-    <row r="589" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="589" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A589" s="15" t="s">
         <v>3886</v>
       </c>
@@ -54665,7 +54737,7 @@
         <v>周锡高 曾丽军</v>
       </c>
     </row>
-    <row r="590" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="590" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A590" s="15" t="s">
         <v>3894</v>
       </c>
@@ -54701,7 +54773,7 @@
         <v/>
       </c>
     </row>
-    <row r="591" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="591" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A591" s="15" t="s">
         <v>3898</v>
       </c>
@@ -54743,7 +54815,7 @@
         <v>柯建西</v>
       </c>
     </row>
-    <row r="592" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="592" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A592" s="15" t="s">
         <v>3904</v>
       </c>
@@ -54873,7 +54945,7 @@
         <v>罗明 宋丹丹</v>
       </c>
     </row>
-    <row r="595" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="595" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A595" s="15" t="s">
         <v>3922</v>
       </c>
@@ -54921,7 +54993,7 @@
         <v>李建斌 刘小玲</v>
       </c>
     </row>
-    <row r="596" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="596" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A596" s="15" t="s">
         <v>3931</v>
       </c>
@@ -55045,7 +55117,7 @@
         <v>陈明 罗飞飞</v>
       </c>
     </row>
-    <row r="599" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="599" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A599" s="15" t="s">
         <v>3950</v>
       </c>
@@ -55079,7 +55151,7 @@
         <v/>
       </c>
     </row>
-    <row r="600" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="600" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A600" s="15" t="s">
         <v>3954</v>
       </c>
@@ -55117,7 +55189,7 @@
         <v/>
       </c>
     </row>
-    <row r="601" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="601" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A601" s="15" t="s">
         <v>3960</v>
       </c>
@@ -55155,7 +55227,7 @@
         <v/>
       </c>
     </row>
-    <row r="602" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="602" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A602" s="15" t="s">
         <v>3966</v>
       </c>
@@ -55203,7 +55275,7 @@
         <v>庞瑶瑶 邹韬</v>
       </c>
     </row>
-    <row r="603" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="603" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A603" s="15" t="s">
         <v>3975</v>
       </c>
@@ -55245,7 +55317,7 @@
         <v>邓钊</v>
       </c>
     </row>
-    <row r="604" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="604" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A604" s="15" t="s">
         <v>3981</v>
       </c>
@@ -55283,7 +55355,7 @@
         <v/>
       </c>
     </row>
-    <row r="605" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="605" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A605" s="15" t="s">
         <v>3987</v>
       </c>
@@ -55329,7 +55401,7 @@
         <v>肖明华 贾巧英</v>
       </c>
     </row>
-    <row r="606" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="606" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A606" s="15" t="s">
         <v>3995</v>
       </c>
@@ -55371,7 +55443,7 @@
         <v>曾亮星</v>
       </c>
     </row>
-    <row r="607" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="607" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A607" s="15" t="s">
         <v>4001</v>
       </c>
@@ -55413,7 +55485,7 @@
         <v>宋国军</v>
       </c>
     </row>
-    <row r="608" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="608" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A608" s="15" t="s">
         <v>4007</v>
       </c>
@@ -55461,7 +55533,7 @@
         <v>邱美胜 刘美华</v>
       </c>
     </row>
-    <row r="609" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="609" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A609" s="15" t="s">
         <v>4016</v>
       </c>
@@ -55503,7 +55575,7 @@
         <v>曾群花</v>
       </c>
     </row>
-    <row r="610" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="610" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A610" s="15" t="s">
         <v>4022</v>
       </c>
@@ -55535,7 +55607,7 @@
         <v/>
       </c>
     </row>
-    <row r="611" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="611" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A611" s="15" t="s">
         <v>4025</v>
       </c>
@@ -55577,7 +55649,7 @@
         <v>赵慧平</v>
       </c>
     </row>
-    <row r="612" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="612" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A612" s="15" t="s">
         <v>4031</v>
       </c>
@@ -55611,7 +55683,7 @@
         <v/>
       </c>
     </row>
-    <row r="613" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="613" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A613" s="15" t="s">
         <v>4035</v>
       </c>
@@ -55649,7 +55721,7 @@
         <v/>
       </c>
     </row>
-    <row r="614" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="614" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A614" s="15" t="s">
         <v>4041</v>
       </c>
@@ -55687,7 +55759,7 @@
         <v/>
       </c>
     </row>
-    <row r="615" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="615" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A615" s="15" t="s">
         <v>4047</v>
       </c>
@@ -55733,7 +55805,7 @@
         <v>郭生姑 李志云</v>
       </c>
     </row>
-    <row r="616" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="616" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A616" s="15" t="s">
         <v>4055</v>
       </c>
@@ -55767,7 +55839,7 @@
         <v/>
       </c>
     </row>
-    <row r="617" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="617" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A617" s="15" t="s">
         <v>4059</v>
       </c>
@@ -55815,7 +55887,7 @@
         <v>潘明圣 谢美艳</v>
       </c>
     </row>
-    <row r="618" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="618" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A618" s="15" t="s">
         <v>4068</v>
       </c>
@@ -55899,7 +55971,7 @@
         <v>胡悦 曾广鑫</v>
       </c>
     </row>
-    <row r="620" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="620" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A620" s="15" t="s">
         <v>4081</v>
       </c>
@@ -55941,7 +56013,7 @@
         <v>欧阳琼</v>
       </c>
     </row>
-    <row r="621" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="621" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A621" s="15" t="s">
         <v>4087</v>
       </c>
@@ -55983,7 +56055,7 @@
         <v>胡玥容</v>
       </c>
     </row>
-    <row r="622" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="622" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A622" s="15" t="s">
         <v>4093</v>
       </c>
@@ -56025,7 +56097,7 @@
         <v>郭乙航</v>
       </c>
     </row>
-    <row r="623" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="623" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A623" s="15" t="s">
         <v>4099</v>
       </c>
@@ -56063,7 +56135,7 @@
         <v/>
       </c>
     </row>
-    <row r="624" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="624" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A624" s="15" t="s">
         <v>4105</v>
       </c>
@@ -56105,7 +56177,7 @@
         <v>王小雪</v>
       </c>
     </row>
-    <row r="625" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="625" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A625" s="15" t="s">
         <v>4111</v>
       </c>
@@ -56151,7 +56223,7 @@
         <v>吴细凤 胡财保</v>
       </c>
     </row>
-    <row r="626" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="626" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A626" s="15" t="s">
         <v>4119</v>
       </c>
@@ -56187,7 +56259,7 @@
         <v/>
       </c>
     </row>
-    <row r="627" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="627" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A627" s="15" t="s">
         <v>4120</v>
       </c>
@@ -56227,7 +56299,7 @@
         <v>张丽华</v>
       </c>
     </row>
-    <row r="628" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="628" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A628" s="15" t="s">
         <v>4126</v>
       </c>
@@ -56275,7 +56347,7 @@
         <v>肖兰平 胡苏平</v>
       </c>
     </row>
-    <row r="629" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="629" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A629" s="15" t="s">
         <v>4130</v>
       </c>
@@ -56323,7 +56395,7 @@
         <v>肖兰平 胡苏平</v>
       </c>
     </row>
-    <row r="630" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="630" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A630" s="15" t="s">
         <v>4132</v>
       </c>
@@ -56365,7 +56437,7 @@
         <v>吉安华通物流中心有限公司</v>
       </c>
     </row>
-    <row r="631" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="631" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A631" s="15" t="s">
         <v>4138</v>
       </c>
@@ -56407,7 +56479,7 @@
         <v>王兰萍</v>
       </c>
     </row>
-    <row r="632" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="632" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A632" s="15" t="s">
         <v>4144</v>
       </c>
@@ -56455,7 +56527,7 @@
         <v>孙明华 邓芳</v>
       </c>
     </row>
-    <row r="633" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="633" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A633" s="15" t="s">
         <v>4153</v>
       </c>
@@ -56491,7 +56563,7 @@
         <v/>
       </c>
     </row>
-    <row r="634" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="634" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A634" s="15" t="s">
         <v>4158</v>
       </c>
@@ -56525,7 +56597,7 @@
         <v/>
       </c>
     </row>
-    <row r="635" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="635" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A635" s="15" t="s">
         <v>4162</v>
       </c>
@@ -56559,7 +56631,7 @@
         <v/>
       </c>
     </row>
-    <row r="636" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="636" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A636" s="15" t="s">
         <v>4166</v>
       </c>
@@ -56607,7 +56679,7 @@
         <v>何小梅 李京忠</v>
       </c>
     </row>
-    <row r="637" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="637" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A637" s="15" t="s">
         <v>4175</v>
       </c>
@@ -56655,7 +56727,7 @@
         <v>邹建岭 麻丽斯</v>
       </c>
     </row>
-    <row r="638" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="638" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A638" s="15" t="s">
         <v>4184</v>
       </c>
@@ -56697,7 +56769,7 @@
         <v>彭杰</v>
       </c>
     </row>
-    <row r="639" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="639" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A639" s="15" t="s">
         <v>4188</v>
       </c>
@@ -56731,7 +56803,7 @@
         <v/>
       </c>
     </row>
-    <row r="640" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="640" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A640" s="15" t="s">
         <v>4192</v>
       </c>
@@ -56765,7 +56837,7 @@
         <v/>
       </c>
     </row>
-    <row r="641" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="641" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A641" s="15" t="s">
         <v>4196</v>
       </c>
@@ -56813,7 +56885,7 @@
         <v>肖智光 杨平</v>
       </c>
     </row>
-    <row r="642" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="642" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A642" s="15" t="s">
         <v>4205</v>
       </c>
@@ -56855,7 +56927,7 @@
         <v>胡丽凤</v>
       </c>
     </row>
-    <row r="643" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="643" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A643" s="15" t="s">
         <v>4211</v>
       </c>
@@ -56897,7 +56969,7 @@
         <v>杨恒熠</v>
       </c>
     </row>
-    <row r="644" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="644" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A644" s="15" t="s">
         <v>4217</v>
       </c>
@@ -56943,7 +57015,7 @@
         <v>刘美华 陈通元</v>
       </c>
     </row>
-    <row r="645" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="645" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A645" s="15" t="s">
         <v>4224</v>
       </c>
@@ -56985,7 +57057,7 @@
         <v>梁秋茂</v>
       </c>
     </row>
-    <row r="646" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="646" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A646" s="15" t="s">
         <v>4230</v>
       </c>
@@ -57033,7 +57105,7 @@
         <v>李军勇 王头女</v>
       </c>
     </row>
-    <row r="647" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="647" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A647" s="15" t="s">
         <v>4239</v>
       </c>
@@ -57071,7 +57143,7 @@
         <v/>
       </c>
     </row>
-    <row r="648" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="648" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A648" s="15" t="s">
         <v>4245</v>
       </c>
@@ -57105,7 +57177,7 @@
         <v/>
       </c>
     </row>
-    <row r="649" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="649" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A649" s="15" t="s">
         <v>4249</v>
       </c>
@@ -57139,7 +57211,7 @@
         <v/>
       </c>
     </row>
-    <row r="650" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="650" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A650" s="15" t="s">
         <v>4253</v>
       </c>
@@ -57175,7 +57247,7 @@
         <v/>
       </c>
     </row>
-    <row r="651" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="651" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A651" s="15" t="s">
         <v>4258</v>
       </c>
@@ -57221,7 +57293,7 @@
         <v>郭洋 徐健</v>
       </c>
     </row>
-    <row r="652" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="652" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A652" s="15" t="s">
         <v>4266</v>
       </c>
@@ -57267,7 +57339,7 @@
         <v>郭洋 徐健</v>
       </c>
     </row>
-    <row r="653" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="653" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A653" s="15" t="s">
         <v>4268</v>
       </c>
@@ -57313,7 +57385,7 @@
         <v>郭君花 胡春凯</v>
       </c>
     </row>
-    <row r="654" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="654" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A654" s="15" t="s">
         <v>4276</v>
       </c>
@@ -57359,7 +57431,7 @@
         <v>郭君花 胡春凯</v>
       </c>
     </row>
-    <row r="655" spans="1:15" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="655" spans="1:15" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A655" s="15" t="s">
         <v>4278</v>
       </c>
@@ -57405,7 +57477,7 @@
         <v>傅欢 刘家华</v>
       </c>
     </row>
-    <row r="656" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="656" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A656" s="15" t="s">
         <v>4283</v>
       </c>
@@ -57447,7 +57519,7 @@
         <v>刘攀</v>
       </c>
     </row>
-    <row r="657" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="657" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A657" s="15" t="s">
         <v>4289</v>
       </c>
@@ -57489,7 +57561,7 @@
         <v>杨志星</v>
       </c>
     </row>
-    <row r="658" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="658" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A658" s="15" t="s">
         <v>4295</v>
       </c>
@@ -57537,7 +57609,7 @@
         <v>石朝军 肖美凤</v>
       </c>
     </row>
-    <row r="659" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="659" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A659" s="15" t="s">
         <v>4304</v>
       </c>
@@ -57583,7 +57655,7 @@
         <v>刘木法 梁茶花</v>
       </c>
     </row>
-    <row r="660" spans="1:15" ht="29.1" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="660" spans="1:15" ht="29.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A660" s="15" t="s">
         <v>4312</v>
       </c>
@@ -57623,7 +57695,7 @@
         <v/>
       </c>
     </row>
-    <row r="661" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="661" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A661" s="15" t="s">
         <v>4318</v>
       </c>
@@ -57665,7 +57737,7 @@
         <v>陈嘉怡</v>
       </c>
     </row>
-    <row r="662" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="662" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A662" s="15" t="s">
         <v>4324</v>
       </c>
@@ -57713,7 +57785,7 @@
         <v>兰成 李楠</v>
       </c>
     </row>
-    <row r="663" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="663" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A663" s="15" t="s">
         <v>4333</v>
       </c>
@@ -57761,7 +57833,7 @@
         <v>傅维成 段旭慧</v>
       </c>
     </row>
-    <row r="664" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="664" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A664" s="15" t="s">
         <v>4342</v>
       </c>
@@ -57803,7 +57875,7 @@
         <v>邓连珠</v>
       </c>
     </row>
-    <row r="665" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="665" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A665" s="15" t="s">
         <v>4348</v>
       </c>
@@ -57849,7 +57921,7 @@
         <v>罗梨 李显海</v>
       </c>
     </row>
-    <row r="666" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="666" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A666" s="15" t="s">
         <v>4356</v>
       </c>
@@ -57891,7 +57963,7 @@
         <v>刘毓</v>
       </c>
     </row>
-    <row r="667" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="667" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A667" s="15" t="s">
         <v>4362</v>
       </c>
@@ -57929,7 +58001,7 @@
         <v/>
       </c>
     </row>
-    <row r="668" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="668" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A668" s="15" t="s">
         <v>4364</v>
       </c>
@@ -57967,7 +58039,7 @@
         <v/>
       </c>
     </row>
-    <row r="669" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="669" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A669" s="15" t="s">
         <v>4365</v>
       </c>
@@ -58005,7 +58077,7 @@
         <v/>
       </c>
     </row>
-    <row r="670" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="670" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A670" s="15" t="s">
         <v>4371</v>
       </c>
@@ -58039,7 +58111,7 @@
         <v/>
       </c>
     </row>
-    <row r="671" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="671" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A671" s="15" t="s">
         <v>4375</v>
       </c>
@@ -58075,7 +58147,7 @@
         <v/>
       </c>
     </row>
-    <row r="672" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="672" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A672" s="15" t="s">
         <v>4380</v>
       </c>
@@ -58113,7 +58185,7 @@
         <v/>
       </c>
     </row>
-    <row r="673" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="673" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A673" s="15" t="s">
         <v>4386</v>
       </c>
@@ -58151,7 +58223,7 @@
         <v/>
       </c>
     </row>
-    <row r="674" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="674" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A674" s="15" t="s">
         <v>4392</v>
       </c>
@@ -58185,7 +58257,7 @@
         <v/>
       </c>
     </row>
-    <row r="675" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="675" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A675" s="15" t="s">
         <v>4396</v>
       </c>
@@ -58227,7 +58299,7 @@
         <v>张世荃</v>
       </c>
     </row>
-    <row r="676" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="676" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A676" s="15" t="s">
         <v>4402</v>
       </c>
@@ -58265,7 +58337,7 @@
         <v/>
       </c>
     </row>
-    <row r="677" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="677" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A677" s="15" t="s">
         <v>4408</v>
       </c>
@@ -58303,7 +58375,7 @@
         <v/>
       </c>
     </row>
-    <row r="678" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="678" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A678" s="15" t="s">
         <v>4413</v>
       </c>
@@ -58341,7 +58413,7 @@
         <v/>
       </c>
     </row>
-    <row r="679" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="679" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A679" s="15" t="s">
         <v>4419</v>
       </c>
@@ -58379,7 +58451,7 @@
         <v/>
       </c>
     </row>
-    <row r="680" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="680" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A680" s="15" t="s">
         <v>4425</v>
       </c>
@@ -58413,7 +58485,7 @@
         <v/>
       </c>
     </row>
-    <row r="681" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="681" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A681" s="15" t="s">
         <v>4429</v>
       </c>
@@ -58451,7 +58523,7 @@
         <v/>
       </c>
     </row>
-    <row r="682" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="682" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A682" s="15" t="s">
         <v>4435</v>
       </c>
@@ -58489,7 +58561,7 @@
         <v/>
       </c>
     </row>
-    <row r="683" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="683" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A683" s="15" t="s">
         <v>4441</v>
       </c>
@@ -58527,7 +58599,7 @@
         <v/>
       </c>
     </row>
-    <row r="684" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="684" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A684" s="15" t="s">
         <v>4447</v>
       </c>
@@ -58563,7 +58635,7 @@
         <v/>
       </c>
     </row>
-    <row r="685" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="685" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A685" s="15" t="s">
         <v>4452</v>
       </c>
@@ -58599,7 +58671,7 @@
         <v/>
       </c>
     </row>
-    <row r="686" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="686" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A686" s="15" t="s">
         <v>4457</v>
       </c>
@@ -58631,7 +58703,7 @@
         <v/>
       </c>
     </row>
-    <row r="687" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="687" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A687" s="15" t="s">
         <v>4460</v>
       </c>
@@ -58663,7 +58735,7 @@
         <v/>
       </c>
     </row>
-    <row r="688" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="688" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A688" s="15" t="s">
         <v>4463</v>
       </c>
@@ -58705,7 +58777,7 @@
         <v>刘建仁</v>
       </c>
     </row>
-    <row r="689" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="689" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A689" s="15" t="s">
         <v>4469</v>
       </c>
@@ -58747,7 +58819,7 @@
         <v>张金香</v>
       </c>
     </row>
-    <row r="690" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="690" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A690" s="15" t="s">
         <v>4475</v>
       </c>
@@ -58793,7 +58865,7 @@
         <v>刘丹 丁玉勇</v>
       </c>
     </row>
-    <row r="691" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="691" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A691" s="15" t="s">
         <v>4483</v>
       </c>
@@ -58829,7 +58901,7 @@
         <v/>
       </c>
     </row>
-    <row r="692" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="692" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A692" s="15" t="s">
         <v>4488</v>
       </c>
@@ -58863,7 +58935,7 @@
         <v/>
       </c>
     </row>
-    <row r="693" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="693" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A693" s="15" t="s">
         <v>4492</v>
       </c>
@@ -58897,7 +58969,7 @@
         <v/>
       </c>
     </row>
-    <row r="694" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="694" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A694" s="15"/>
       <c r="B694" s="6" t="s">
         <v>4496</v>
@@ -58929,7 +59001,7 @@
         <v/>
       </c>
     </row>
-    <row r="695" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="695" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A695" s="15" t="s">
         <v>4499</v>
       </c>
@@ -58967,7 +59039,7 @@
         <v/>
       </c>
     </row>
-    <row r="696" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="696" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A696" s="15" t="s">
         <v>4505</v>
       </c>
@@ -59014,7 +59086,7 @@
 刘友庭</v>
       </c>
     </row>
-    <row r="697" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="697" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A697" s="15" t="s">
         <v>4512</v>
       </c>
@@ -59060,7 +59132,7 @@
         <v>刘娟 周羽</v>
       </c>
     </row>
-    <row r="698" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="698" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A698" s="15" t="s">
         <v>4520</v>
       </c>
@@ -59094,7 +59166,7 @@
         <v/>
       </c>
     </row>
-    <row r="699" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="699" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A699" s="15" t="s">
         <v>4524</v>
       </c>
@@ -59136,7 +59208,7 @@
         <v>刘娇娇</v>
       </c>
     </row>
-    <row r="700" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="700" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A700" s="15" t="s">
         <v>4530</v>
       </c>
@@ -59184,7 +59256,7 @@
         <v>张琦 易利民</v>
       </c>
     </row>
-    <row r="701" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="701" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A701" s="15" t="s">
         <v>4539</v>
       </c>
@@ -59222,7 +59294,7 @@
         <v/>
       </c>
     </row>
-    <row r="702" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="702" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A702" s="15" t="s">
         <v>4545</v>
       </c>
@@ -59258,7 +59330,7 @@
         <v/>
       </c>
     </row>
-    <row r="703" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="703" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A703" s="15" t="s">
         <v>4550</v>
       </c>
@@ -59296,7 +59368,7 @@
         <v/>
       </c>
     </row>
-    <row r="704" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="704" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A704" s="15" t="s">
         <v>4556</v>
       </c>
@@ -59334,7 +59406,7 @@
         <v/>
       </c>
     </row>
-    <row r="705" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="705" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A705" s="15" t="s">
         <v>4562</v>
       </c>
@@ -59370,7 +59442,7 @@
         <v/>
       </c>
     </row>
-    <row r="706" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="706" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A706" s="15" t="s">
         <v>4567</v>
       </c>
@@ -59404,7 +59476,7 @@
         <v/>
       </c>
     </row>
-    <row r="707" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="707" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A707" s="15" t="s">
         <v>4571</v>
       </c>
@@ -59446,7 +59518,7 @@
         <v>王锋</v>
       </c>
     </row>
-    <row r="708" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="708" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A708" s="15" t="s">
         <v>4574</v>
       </c>
@@ -59480,7 +59552,7 @@
         <v/>
       </c>
     </row>
-    <row r="709" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="709" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A709" s="15" t="s">
         <v>4578</v>
       </c>
@@ -59518,7 +59590,7 @@
         <v/>
       </c>
     </row>
-    <row r="710" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="710" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A710" s="15" t="s">
         <v>4584</v>
       </c>
@@ -59552,7 +59624,7 @@
         <v/>
       </c>
     </row>
-    <row r="711" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="711" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A711" s="15" t="s">
         <v>4588</v>
       </c>
@@ -59598,7 +59670,7 @@
         <v>黄丽 刘忠文</v>
       </c>
     </row>
-    <row r="712" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="712" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A712" s="15" t="s">
         <v>4595</v>
       </c>
@@ -59644,7 +59716,7 @@
         <v>邱刚 陈筠</v>
       </c>
     </row>
-    <row r="713" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="713" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A713" s="15" t="s">
         <v>4603</v>
       </c>
@@ -59688,7 +59760,7 @@
         <v>周杰云 刘足凤</v>
       </c>
     </row>
-    <row r="714" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="714" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A714" s="15" t="s">
         <v>4611</v>
       </c>
@@ -59728,7 +59800,7 @@
         <v>万丽</v>
       </c>
     </row>
-    <row r="715" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="715" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A715" s="15" t="s">
         <v>4617</v>
       </c>
@@ -59768,7 +59840,7 @@
         <v>欧阳小璇</v>
       </c>
     </row>
-    <row r="716" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="716" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A716" s="15" t="s">
         <v>4623</v>
       </c>
@@ -59808,7 +59880,7 @@
         <v>周正英</v>
       </c>
     </row>
-    <row r="717" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="717" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A717" s="15" t="s">
         <v>4629</v>
       </c>
@@ -59848,7 +59920,7 @@
         <v>宋国珍</v>
       </c>
     </row>
-    <row r="718" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="718" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A718" s="15" t="s">
         <v>4635</v>
       </c>
@@ -59888,7 +59960,7 @@
         <v>黄承旭</v>
       </c>
     </row>
-    <row r="719" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="719" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A719" s="15" t="s">
         <v>4641</v>
       </c>
@@ -59932,7 +60004,7 @@
         <v>夏瑶 许扬坤</v>
       </c>
     </row>
-    <row r="720" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="720" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A720" s="15" t="s">
         <v>4649</v>
       </c>
@@ -59976,7 +60048,7 @@
         <v>周好英 罗秋基</v>
       </c>
     </row>
-    <row r="721" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="721" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A721" s="15" t="s">
         <v>4657</v>
       </c>
@@ -60020,7 +60092,7 @@
         <v>王淑风 胡椿之</v>
       </c>
     </row>
-    <row r="722" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="722" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A722" s="15" t="s">
         <v>4665</v>
       </c>
@@ -60060,7 +60132,7 @@
         <v>曾庆铭</v>
       </c>
     </row>
-    <row r="723" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="723" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A723" s="15" t="s">
         <v>4671</v>
       </c>
@@ -60102,7 +60174,7 @@
         <v>夏天珺</v>
       </c>
     </row>
-    <row r="724" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="724" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A724" s="15" t="s">
         <v>4677</v>
       </c>
@@ -60140,7 +60212,7 @@
         <v/>
       </c>
     </row>
-    <row r="725" spans="1:15" ht="40.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="725" spans="1:15" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A725" s="15" t="s">
         <v>4683</v>
       </c>
@@ -60176,7 +60248,7 @@
         <v/>
       </c>
     </row>
-    <row r="726" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="726" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A726" s="15" t="s">
         <v>4688</v>
       </c>
@@ -60208,7 +60280,7 @@
         <v/>
       </c>
     </row>
-    <row r="727" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
+    <row r="727" spans="1:15" ht="54" x14ac:dyDescent="0.15">
       <c r="A727" s="15" t="s">
         <v>4691</v>
       </c>
@@ -60254,7 +60326,7 @@
         <v>肖兰平 胡苏平</v>
       </c>
     </row>
-    <row r="728" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
+    <row r="728" spans="1:15" ht="54" x14ac:dyDescent="0.15">
       <c r="A728" s="15" t="s">
         <v>4694</v>
       </c>
@@ -60300,7 +60372,7 @@
         <v>肖兰平 胡苏平</v>
       </c>
     </row>
-    <row r="729" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="729" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A729" s="3" t="s">
         <v>4696</v>
       </c>
@@ -60334,7 +60406,7 @@
         <v/>
       </c>
     </row>
-    <row r="730" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="730" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A730" s="15" t="s">
         <v>4700</v>
       </c>
@@ -60374,7 +60446,7 @@
         <v/>
       </c>
     </row>
-    <row r="731" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="731" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A731" s="15" t="s">
         <v>4707</v>
       </c>
@@ -60408,7 +60480,7 @@
         <v/>
       </c>
     </row>
-    <row r="732" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="732" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A732" s="15" t="s">
         <v>4710</v>
       </c>
@@ -60442,7 +60514,7 @@
         <v/>
       </c>
     </row>
-    <row r="733" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="733" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A733" s="15" t="s">
         <v>4714</v>
       </c>
@@ -60482,7 +60554,7 @@
         <v/>
       </c>
     </row>
-    <row r="734" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="734" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A734" s="15"/>
       <c r="B734" s="6" t="s">
         <v>4721</v>
@@ -60526,7 +60598,7 @@
         <v>谢世平 张开燕</v>
       </c>
     </row>
-    <row r="735" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="735" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A735" s="15" t="s">
         <v>4728</v>
       </c>
@@ -60574,7 +60646,7 @@
         <v>朱小兵 肖菊月</v>
       </c>
     </row>
-    <row r="736" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="736" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A736" s="15" t="s">
         <v>4736</v>
       </c>
@@ -60616,7 +60688,7 @@
         <v>刘秋芳</v>
       </c>
     </row>
-    <row r="737" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
+    <row r="737" spans="1:15" ht="54" x14ac:dyDescent="0.15">
       <c r="A737" s="15" t="s">
         <v>4742</v>
       </c>
@@ -60662,7 +60734,7 @@
         <v>王燕萍 李文军</v>
       </c>
     </row>
-    <row r="738" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="738" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A738" s="15" t="s">
         <v>4745</v>
       </c>
@@ -60694,7 +60766,7 @@
         <v/>
       </c>
     </row>
-    <row r="739" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="739" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A739" s="15" t="s">
         <v>4748</v>
       </c>
@@ -60730,7 +60802,7 @@
         <v/>
       </c>
     </row>
-    <row r="740" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
+    <row r="740" spans="1:15" ht="54" x14ac:dyDescent="0.15">
       <c r="A740" s="15" t="s">
         <v>4753</v>
       </c>
@@ -60778,7 +60850,7 @@
         <v>王青花 刘本兴</v>
       </c>
     </row>
-    <row r="741" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="741" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A741" s="15" t="s">
         <v>4756</v>
       </c>
@@ -60820,7 +60892,7 @@
         <v>龙晓萍</v>
       </c>
     </row>
-    <row r="742" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="742" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A742" s="15" t="s">
         <v>4762</v>
       </c>
@@ -60862,7 +60934,7 @@
         <v>肖雅清</v>
       </c>
     </row>
-    <row r="743" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="743" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A743" s="15" t="s">
         <v>4768</v>
       </c>
@@ -60896,7 +60968,7 @@
         <v/>
       </c>
     </row>
-    <row r="744" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="744" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A744" s="15" t="s">
         <v>4772</v>
       </c>
@@ -60934,7 +61006,7 @@
         <v/>
       </c>
     </row>
-    <row r="745" spans="1:15" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="745" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A745" s="15" t="s">
         <v>4778</v>
       </c>
@@ -60972,7 +61044,7 @@
         <v/>
       </c>
     </row>
-    <row r="746" spans="1:15" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="746" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A746" s="15" t="s">
         <v>4784</v>
       </c>
@@ -61006,7 +61078,7 @@
         <v/>
       </c>
     </row>
-    <row r="747" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="747" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A747" s="15" t="s">
         <v>4788</v>
       </c>
@@ -61054,7 +61126,7 @@
         <v>江世林 吴秀兰</v>
       </c>
     </row>
-    <row r="748" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="748" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A748" s="15" t="s">
         <v>4797</v>
       </c>
@@ -61096,7 +61168,7 @@
         <v>张轩铭</v>
       </c>
     </row>
-    <row r="749" spans="1:15" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="749" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A749" s="15" t="s">
         <v>4803</v>
       </c>
@@ -61144,7 +61216,7 @@
         <v>刘瑛 肖海</v>
       </c>
     </row>
-    <row r="750" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="750" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A750" s="15" t="s">
         <v>4812</v>
       </c>
@@ -61190,7 +61262,7 @@
         <v>梁长征 胡冬英</v>
       </c>
     </row>
-    <row r="751" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="751" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A751" s="15" t="s">
         <v>4816</v>
       </c>
@@ -61226,7 +61298,7 @@
         <v/>
       </c>
     </row>
-    <row r="752" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="752" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A752" s="15" t="s">
         <v>4821</v>
       </c>
@@ -61262,7 +61334,7 @@
         <v/>
       </c>
     </row>
-    <row r="753" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="753" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A753" s="15" t="s">
         <v>4826</v>
       </c>
@@ -61294,7 +61366,7 @@
         <v/>
       </c>
     </row>
-    <row r="754" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="754" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A754" s="15" t="s">
         <v>4829</v>
       </c>
@@ -61326,7 +61398,7 @@
         <v/>
       </c>
     </row>
-    <row r="755" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="755" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A755" s="15" t="s">
         <v>4832</v>
       </c>
@@ -61358,7 +61430,7 @@
         <v/>
       </c>
     </row>
-    <row r="756" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
+    <row r="756" spans="1:15" ht="54" x14ac:dyDescent="0.15">
       <c r="A756" s="15" t="s">
         <v>4835</v>
       </c>
@@ -61404,7 +61476,7 @@
         <v>汪小慧 刘轶星</v>
       </c>
     </row>
-    <row r="757" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="757" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A757" s="15" t="s">
         <v>4839</v>
       </c>
@@ -61444,7 +61516,7 @@
         <v>高义茂</v>
       </c>
     </row>
-    <row r="758" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="758" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A758" s="15" t="s">
         <v>4845</v>
       </c>
@@ -61488,7 +61560,7 @@
         <v>康博文 邓燕</v>
       </c>
     </row>
-    <row r="759" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="759" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A759" s="15" t="s">
         <v>4853</v>
       </c>
@@ -61616,7 +61688,7 @@
         <v>李豫西</v>
       </c>
     </row>
-    <row r="762" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="762" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A762" s="15" t="s">
         <v>4874</v>
       </c>
@@ -61658,7 +61730,7 @@
         <v>曹新陈</v>
       </c>
     </row>
-    <row r="763" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="763" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A763" s="15" t="s">
         <v>4880</v>
       </c>
@@ -61706,7 +61778,7 @@
         <v>钱志朋 曾雪薇</v>
       </c>
     </row>
-    <row r="764" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="764" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A764" s="15" t="s">
         <v>4889</v>
       </c>
@@ -61754,7 +61826,7 @@
         <v>廖芬秀 吴富喜</v>
       </c>
     </row>
-    <row r="765" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="765" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A765" s="15" t="s">
         <v>4898</v>
       </c>
@@ -61796,7 +61868,7 @@
         <v>周小燕</v>
       </c>
     </row>
-    <row r="766" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="766" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A766" s="15" t="s">
         <v>4903</v>
       </c>
@@ -61844,7 +61916,7 @@
         <v>伍继先 胡小青</v>
       </c>
     </row>
-    <row r="767" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="767" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A767" s="15" t="s">
         <v>4911</v>
       </c>
@@ -61882,7 +61954,7 @@
         <v/>
       </c>
     </row>
-    <row r="768" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="768" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A768" s="15" t="s">
         <v>4917</v>
       </c>
@@ -61920,7 +61992,7 @@
         <v/>
       </c>
     </row>
-    <row r="769" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="769" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A769" s="15" t="s">
         <v>4923</v>
       </c>
@@ -61954,7 +62026,7 @@
         <v/>
       </c>
     </row>
-    <row r="770" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="770" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A770" s="15" t="s">
         <v>4927</v>
       </c>
@@ -61994,7 +62066,7 @@
         <v>钟青</v>
       </c>
     </row>
-    <row r="771" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="771" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A771" s="15" t="s">
         <v>4931</v>
       </c>
@@ -62040,7 +62112,7 @@
         <v>李民 张园园</v>
       </c>
     </row>
-    <row r="772" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="772" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A772" s="15" t="s">
         <v>4939</v>
       </c>
@@ -62076,7 +62148,7 @@
         <v/>
       </c>
     </row>
-    <row r="773" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="773" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A773" s="15" t="s">
         <v>4944</v>
       </c>
@@ -62122,7 +62194,7 @@
         <v>周水英 焦大保</v>
       </c>
     </row>
-    <row r="774" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="774" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A774" s="15" t="s">
         <v>4952</v>
       </c>
@@ -62164,7 +62236,7 @@
         <v>洪鑫</v>
       </c>
     </row>
-    <row r="775" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="775" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A775" s="15" t="s">
         <v>4955</v>
       </c>
@@ -62210,7 +62282,7 @@
         <v>姜伟和 龙慧</v>
       </c>
     </row>
-    <row r="776" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="776" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A776" s="15" t="s">
         <v>4963</v>
       </c>
@@ -62254,7 +62326,7 @@
         <v>黄冬鸣 裴露</v>
       </c>
     </row>
-    <row r="777" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="777" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A777" s="15" t="s">
         <v>4971</v>
       </c>
@@ -62302,7 +62374,7 @@
         <v>李志红 魏立民</v>
       </c>
     </row>
-    <row r="778" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="778" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A778" s="15" t="s">
         <v>4976</v>
       </c>
@@ -62344,7 +62416,7 @@
         <v>徐磊</v>
       </c>
     </row>
-    <row r="779" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="779" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A779" s="15" t="s">
         <v>4982</v>
       </c>
@@ -62380,7 +62452,7 @@
         <v/>
       </c>
     </row>
-    <row r="780" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="780" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A780" s="15" t="s">
         <v>4987</v>
       </c>
@@ -62412,7 +62484,7 @@
         <v/>
       </c>
     </row>
-    <row r="781" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="781" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A781" s="15" t="s">
         <v>4990</v>
       </c>
@@ -62446,7 +62518,7 @@
         <v/>
       </c>
     </row>
-    <row r="782" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="782" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A782" s="15" t="s">
         <v>4994</v>
       </c>
@@ -62490,7 +62562,7 @@
         <v/>
       </c>
     </row>
-    <row r="783" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="783" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A783" s="15" t="s">
         <v>4995</v>
       </c>
@@ -62530,7 +62602,7 @@
         <v>曾美君</v>
       </c>
     </row>
-    <row r="784" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="784" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A784" s="15" t="s">
         <v>5001</v>
       </c>
@@ -62570,7 +62642,7 @@
         <v>蒋力</v>
       </c>
     </row>
-    <row r="785" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="785" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A785" s="15" t="s">
         <v>5007</v>
       </c>
@@ -62616,7 +62688,7 @@
         <v>李艳红 陈林</v>
       </c>
     </row>
-    <row r="786" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="786" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A786" s="15" t="s">
         <v>5016</v>
       </c>
@@ -62660,7 +62732,7 @@
         <v>钟新香 王华</v>
       </c>
     </row>
-    <row r="787" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="787" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A787" s="15" t="s">
         <v>5024</v>
       </c>
@@ -62708,7 +62780,7 @@
         <v>刘志强 王飞丽</v>
       </c>
     </row>
-    <row r="788" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="788" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A788" s="15" t="s">
         <v>5033</v>
       </c>
@@ -62752,7 +62824,7 @@
         <v>罗师凤 郭长俊</v>
       </c>
     </row>
-    <row r="789" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="789" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A789" s="15" t="s">
         <v>5041</v>
       </c>
@@ -62792,7 +62864,7 @@
         <v>胡慧</v>
       </c>
     </row>
-    <row r="790" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="790" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A790" s="15" t="s">
         <v>5047</v>
       </c>
@@ -62840,7 +62912,7 @@
         <v>肖文军 刘小丽</v>
       </c>
     </row>
-    <row r="791" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="791" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A791" s="15" t="s">
         <v>5056</v>
       </c>
@@ -62888,7 +62960,7 @@
         <v>欧阳艳凤 郭文熹</v>
       </c>
     </row>
-    <row r="792" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="792" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A792" s="15" t="s">
         <v>5065</v>
       </c>
@@ -62936,7 +63008,7 @@
         <v>胡海佩 王文明</v>
       </c>
     </row>
-    <row r="793" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="793" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A793" s="15" t="s">
         <v>5074</v>
       </c>
@@ -62978,7 +63050,7 @@
         <v>陈伟华</v>
       </c>
     </row>
-    <row r="794" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="794" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A794" s="15" t="s">
         <v>5080</v>
       </c>
@@ -63018,7 +63090,7 @@
         <v>王娜</v>
       </c>
     </row>
-    <row r="795" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="795" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A795" s="15" t="s">
         <v>5086</v>
       </c>
@@ -63058,7 +63130,7 @@
         <v>罗小芳</v>
       </c>
     </row>
-    <row r="796" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="796" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A796" s="15" t="s">
         <v>5092</v>
       </c>
@@ -63102,7 +63174,7 @@
         <v>王头法 罗根媖</v>
       </c>
     </row>
-    <row r="797" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="797" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A797" s="15" t="s">
         <v>5100</v>
       </c>
@@ -63146,7 +63218,7 @@
         <v>张六妹 胡桂成</v>
       </c>
     </row>
-    <row r="798" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="798" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A798" s="15" t="s">
         <v>5108</v>
       </c>
@@ -63184,7 +63256,7 @@
         <v/>
       </c>
     </row>
-    <row r="799" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
+    <row r="799" spans="1:15" ht="54" x14ac:dyDescent="0.15">
       <c r="A799" s="15" t="s">
         <v>5114</v>
       </c>
@@ -63230,7 +63302,7 @@
         <v>廖荣英 邹继华</v>
       </c>
     </row>
-    <row r="800" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="800" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A800" s="15" t="s">
         <v>5118</v>
       </c>
@@ -63268,7 +63340,7 @@
         <v/>
       </c>
     </row>
-    <row r="801" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="801" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A801" s="15" t="s">
         <v>5124</v>
       </c>
@@ -63302,7 +63374,7 @@
         <v/>
       </c>
     </row>
-    <row r="802" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="802" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A802" s="15" t="s">
         <v>5128</v>
       </c>
@@ -63340,7 +63412,7 @@
         <v/>
       </c>
     </row>
-    <row r="803" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="803" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A803" s="15" t="s">
         <v>5134</v>
       </c>
@@ -63374,7 +63446,7 @@
         <v/>
       </c>
     </row>
-    <row r="804" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="804" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A804" s="15" t="s">
         <v>5138</v>
       </c>
@@ -63412,7 +63484,7 @@
         <v/>
       </c>
     </row>
-    <row r="805" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="805" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A805" s="15" t="s">
         <v>5144</v>
       </c>
@@ -63450,7 +63522,7 @@
         <v/>
       </c>
     </row>
-    <row r="806" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="806" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A806" s="15" t="s">
         <v>5150</v>
       </c>
@@ -63492,7 +63564,7 @@
         <v/>
       </c>
     </row>
-    <row r="807" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="807" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A807" s="15" t="s">
         <v>5151</v>
       </c>
@@ -63530,7 +63602,7 @@
         <v/>
       </c>
     </row>
-    <row r="808" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="808" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A808" s="15" t="s">
         <v>5152</v>
       </c>
@@ -63566,7 +63638,7 @@
         <v/>
       </c>
     </row>
-    <row r="809" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="809" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A809" s="15" t="s">
         <v>5157</v>
       </c>
@@ -63612,7 +63684,7 @@
         <v>李春华 郭厚河</v>
       </c>
     </row>
-    <row r="810" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="810" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A810" s="15" t="s">
         <v>5165</v>
       </c>
@@ -63660,7 +63732,7 @@
         <v>尹嵩 姚文娟</v>
       </c>
     </row>
-    <row r="811" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="811" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A811" s="15" t="s">
         <v>5174</v>
       </c>
@@ -63708,7 +63780,7 @@
         <v>胡秋妹 张锋兴</v>
       </c>
     </row>
-    <row r="812" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="812" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A812" s="15" t="s">
         <v>5183</v>
       </c>
@@ -63750,7 +63822,7 @@
         <v>朱莎</v>
       </c>
     </row>
-    <row r="813" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="813" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A813" s="15" t="s">
         <v>5189</v>
       </c>
@@ -63790,7 +63862,7 @@
         <v>杨婧</v>
       </c>
     </row>
-    <row r="814" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="814" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A814" s="15" t="s">
         <v>5195</v>
       </c>
@@ -63830,7 +63902,7 @@
         <v>谢同峰</v>
       </c>
     </row>
-    <row r="815" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="815" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A815" s="15" t="s">
         <v>5201</v>
       </c>
@@ -63870,7 +63942,7 @@
         <v>刘倩文</v>
       </c>
     </row>
-    <row r="816" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="816" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A816" s="15" t="s">
         <v>5207</v>
       </c>
@@ -63910,7 +63982,7 @@
         <v>张秋萍</v>
       </c>
     </row>
-    <row r="817" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="817" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A817" s="15" t="s">
         <v>5213</v>
       </c>
@@ -63956,7 +64028,7 @@
         <v>罗根华 王燕华</v>
       </c>
     </row>
-    <row r="818" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
+    <row r="818" spans="1:15" ht="54" x14ac:dyDescent="0.15">
       <c r="A818" s="15" t="s">
         <v>5221</v>
       </c>
@@ -64004,7 +64076,7 @@
         <v>黄兵 戴智芳</v>
       </c>
     </row>
-    <row r="819" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
+    <row r="819" spans="1:15" ht="54" x14ac:dyDescent="0.15">
       <c r="A819" s="15" t="s">
         <v>5230</v>
       </c>
@@ -64052,7 +64124,7 @@
         <v>黄兵 戴智芳</v>
       </c>
     </row>
-    <row r="820" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="820" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A820" s="15"/>
       <c r="B820" s="6" t="s">
         <v>5231</v>
@@ -64086,7 +64158,7 @@
         <v/>
       </c>
     </row>
-    <row r="821" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="821" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A821" s="15" t="s">
         <v>5236</v>
       </c>
@@ -64124,7 +64196,7 @@
         <v/>
       </c>
     </row>
-    <row r="822" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="822" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A822" s="15" t="s">
         <v>5242</v>
       </c>
@@ -64162,7 +64234,7 @@
         <v/>
       </c>
     </row>
-    <row r="823" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="823" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A823" s="15" t="s">
         <v>5243</v>
       </c>
@@ -64204,7 +64276,7 @@
         <v>吴雅荣</v>
       </c>
     </row>
-    <row r="824" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="824" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A824" s="15" t="s">
         <v>5249</v>
       </c>
@@ -64246,7 +64318,7 @@
         <v>翟回乡</v>
       </c>
     </row>
-    <row r="825" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="825" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A825" s="15" t="s">
         <v>5255</v>
       </c>
@@ -64294,7 +64366,7 @@
         <v>陈武 陈玉玲</v>
       </c>
     </row>
-    <row r="826" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="826" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A826" s="15" t="s">
         <v>5264</v>
       </c>
@@ -64336,7 +64408,7 @@
         <v>彭志强</v>
       </c>
     </row>
-    <row r="827" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="827" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A827" s="15" t="s">
         <v>5270</v>
       </c>
@@ -64378,7 +64450,7 @@
         <v>王秀凤</v>
       </c>
     </row>
-    <row r="828" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="828" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A828" s="15" t="s">
         <v>5276</v>
       </c>
@@ -64424,7 +64496,7 @@
         <v>陈燕 王希鹏</v>
       </c>
     </row>
-    <row r="829" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="829" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A829" s="15" t="s">
         <v>5284</v>
       </c>
@@ -64464,7 +64536,7 @@
         <v>欧阳凯松</v>
       </c>
     </row>
-    <row r="830" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="830" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A830" s="15" t="s">
         <v>5290</v>
       </c>
@@ -64512,7 +64584,7 @@
         <v>王良棵 赖琼英</v>
       </c>
     </row>
-    <row r="831" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="831" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A831" s="15" t="s">
         <v>5299</v>
       </c>
@@ -64554,7 +64626,7 @@
         <v>吴杰</v>
       </c>
     </row>
-    <row r="832" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="832" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A832" s="15" t="s">
         <v>5305</v>
       </c>
@@ -64592,7 +64664,7 @@
         <v/>
       </c>
     </row>
-    <row r="833" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="833" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A833" s="15" t="s">
         <v>5311</v>
       </c>
@@ -64630,7 +64702,7 @@
         <v/>
       </c>
     </row>
-    <row r="834" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="834" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A834" s="15" t="s">
         <v>5317</v>
       </c>
@@ -64668,7 +64740,7 @@
         <v/>
       </c>
     </row>
-    <row r="835" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="835" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A835" s="15" t="s">
         <v>5318</v>
       </c>
@@ -64704,7 +64776,7 @@
         <v/>
       </c>
     </row>
-    <row r="836" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="836" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A836" s="15" t="s">
         <v>5323</v>
       </c>
@@ -64742,7 +64814,7 @@
         <v/>
       </c>
     </row>
-    <row r="837" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="837" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A837" s="15" t="s">
         <v>5329</v>
       </c>
@@ -64784,7 +64856,7 @@
         <v>石建涛</v>
       </c>
     </row>
-    <row r="838" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="838" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A838" s="15" t="s">
         <v>5335</v>
       </c>
@@ -64816,7 +64888,7 @@
         <v/>
       </c>
     </row>
-    <row r="839" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="839" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A839" s="15" t="s">
         <v>5338</v>
       </c>
@@ -64858,7 +64930,7 @@
         <v>李文杰</v>
       </c>
     </row>
-    <row r="840" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="840" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A840" s="15" t="s">
         <v>5344</v>
       </c>
@@ -64900,7 +64972,7 @@
         <v>王红勇</v>
       </c>
     </row>
-    <row r="841" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="841" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A841" s="15" t="s">
         <v>5350</v>
       </c>
@@ -64942,7 +65014,7 @@
         <v>李云</v>
       </c>
     </row>
-    <row r="842" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="842" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A842" s="15" t="s">
         <v>5356</v>
       </c>
@@ -64988,7 +65060,7 @@
         <v>刘玉梅 范孝祥</v>
       </c>
     </row>
-    <row r="843" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="843" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A843" s="15" t="s">
         <v>5364</v>
       </c>
@@ -65034,7 +65106,7 @@
         <v>晏志光 刘娟</v>
       </c>
     </row>
-    <row r="844" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="844" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A844" s="15" t="s">
         <v>5372</v>
       </c>
@@ -65076,7 +65148,7 @@
         <v>冯程</v>
       </c>
     </row>
-    <row r="845" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="845" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A845" s="15" t="s">
         <v>5376</v>
       </c>
@@ -65114,7 +65186,7 @@
         <v/>
       </c>
     </row>
-    <row r="846" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="846" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A846" s="15" t="s">
         <v>5382</v>
       </c>
@@ -65152,7 +65224,7 @@
         <v/>
       </c>
     </row>
-    <row r="847" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="847" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A847" s="15" t="s">
         <v>5388</v>
       </c>
@@ -65190,7 +65262,7 @@
         <v/>
       </c>
     </row>
-    <row r="848" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="848" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A848" s="15" t="s">
         <v>5394</v>
       </c>
@@ -65228,7 +65300,7 @@
         <v/>
       </c>
     </row>
-    <row r="849" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="849" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A849" s="15" t="s">
         <v>5400</v>
       </c>
@@ -65266,7 +65338,7 @@
         <v/>
       </c>
     </row>
-    <row r="850" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="850" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A850" s="15" t="s">
         <v>5406</v>
       </c>
@@ -65308,7 +65380,7 @@
         <v>罗家忠</v>
       </c>
     </row>
-    <row r="851" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="851" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A851" s="15" t="s">
         <v>5412</v>
       </c>
@@ -65354,7 +65426,7 @@
         <v>胡智武 谢丹</v>
       </c>
     </row>
-    <row r="852" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="852" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A852" s="15" t="s">
         <v>5415</v>
       </c>
@@ -65400,7 +65472,7 @@
         <v>胡智武 谢丹</v>
       </c>
     </row>
-    <row r="853" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="853" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A853" s="15" t="s">
         <v>5417</v>
       </c>
@@ -65442,7 +65514,7 @@
         <v>邱华英</v>
       </c>
     </row>
-    <row r="854" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="854" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A854" s="15" t="s">
         <v>5423</v>
       </c>
@@ -65528,7 +65600,7 @@
         <v>李展搏 肖苏华</v>
       </c>
     </row>
-    <row r="856" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="856" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A856" s="15" t="s">
         <v>5437</v>
       </c>
@@ -65562,7 +65634,7 @@
         <v/>
       </c>
     </row>
-    <row r="857" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="857" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A857" s="15" t="s">
         <v>5441</v>
       </c>
@@ -65604,7 +65676,7 @@
         <v>段娇琴</v>
       </c>
     </row>
-    <row r="858" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="858" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A858" s="15" t="s">
         <v>5447</v>
       </c>
@@ -65642,7 +65714,7 @@
         <v/>
       </c>
     </row>
-    <row r="859" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="859" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A859" s="15" t="s">
         <v>5453</v>
       </c>
@@ -65690,7 +65762,7 @@
         <v>李丽 谢步兴</v>
       </c>
     </row>
-    <row r="860" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="860" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A860" s="15" t="s">
         <v>5462</v>
       </c>
@@ -65818,7 +65890,7 @@
         <v>王卫红</v>
       </c>
     </row>
-    <row r="863" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="863" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A863" s="15" t="s">
         <v>5484</v>
       </c>
@@ -65858,7 +65930,7 @@
         <v/>
       </c>
     </row>
-    <row r="864" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="864" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A864" s="15" t="s">
         <v>5490</v>
       </c>
@@ -65898,7 +65970,7 @@
         <v>欧阳学海</v>
       </c>
     </row>
-    <row r="865" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="865" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A865" s="15" t="s">
         <v>5496</v>
       </c>
@@ -65942,7 +66014,7 @@
         <v>阮燕芳 赵令辉</v>
       </c>
     </row>
-    <row r="866" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="866" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A866" s="15" t="s">
         <v>5504</v>
       </c>
@@ -65988,7 +66060,7 @@
         <v>刘庆华 吴传柱</v>
       </c>
     </row>
-    <row r="867" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="867" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A867" s="15" t="s">
         <v>5513</v>
       </c>
@@ -66034,7 +66106,7 @@
         <v>陈美青 曹绍剑</v>
       </c>
     </row>
-    <row r="868" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="868" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A868" s="15" t="s">
         <v>5521</v>
       </c>
@@ -66080,7 +66152,7 @@
         <v>陈美青 曹绍剑</v>
       </c>
     </row>
-    <row r="869" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="869" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A869" s="15" t="s">
         <v>5523</v>
       </c>
@@ -66126,7 +66198,7 @@
         <v>康淑萍 刘文军</v>
       </c>
     </row>
-    <row r="870" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="870" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A870" s="15" t="s">
         <v>5531</v>
       </c>
@@ -66168,7 +66240,7 @@
         <v>刘琼</v>
       </c>
     </row>
-    <row r="871" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="871" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A871" s="15" t="s">
         <v>5536</v>
       </c>
@@ -66216,7 +66288,7 @@
         <v>彭武强 邹俊霞</v>
       </c>
     </row>
-    <row r="872" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="872" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A872" s="15" t="s">
         <v>5545</v>
       </c>
@@ -66254,7 +66326,7 @@
         <v/>
       </c>
     </row>
-    <row r="873" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="873" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A873" s="15" t="s">
         <v>5546</v>
       </c>
@@ -66294,7 +66366,7 @@
         <v/>
       </c>
     </row>
-    <row r="874" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="874" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A874" s="15" t="s">
         <v>5553</v>
       </c>
@@ -66338,7 +66410,7 @@
         <v>刘小红 王茨平</v>
       </c>
     </row>
-    <row r="875" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
+    <row r="875" spans="1:15" ht="54" x14ac:dyDescent="0.15">
       <c r="A875" s="15" t="s">
         <v>5561</v>
       </c>
@@ -66384,7 +66456,7 @@
         <v>王树文 马慧娥</v>
       </c>
     </row>
-    <row r="876" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="876" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A876" s="15" t="s">
         <v>5569</v>
       </c>
@@ -66422,7 +66494,7 @@
         <v/>
       </c>
     </row>
-    <row r="877" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="877" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A877" s="15" t="s">
         <v>5575</v>
       </c>
@@ -66456,7 +66528,7 @@
         <v/>
       </c>
     </row>
-    <row r="878" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="878" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A878" s="15" t="s">
         <v>5579</v>
       </c>
@@ -66494,7 +66566,7 @@
         <v/>
       </c>
     </row>
-    <row r="879" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="879" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A879" s="15" t="s">
         <v>5585</v>
       </c>
@@ -66526,7 +66598,7 @@
         <v/>
       </c>
     </row>
-    <row r="880" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="880" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A880" s="15" t="s">
         <v>5588</v>
       </c>
@@ -66558,7 +66630,7 @@
         <v/>
       </c>
     </row>
-    <row r="881" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="881" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A881" s="15" t="s">
         <v>5591</v>
       </c>
@@ -66600,7 +66672,7 @@
         <v>刘佩航</v>
       </c>
     </row>
-    <row r="882" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="882" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A882" s="15" t="s">
         <v>5597</v>
       </c>
@@ -66646,7 +66718,7 @@
         <v>彭丽 王超</v>
       </c>
     </row>
-    <row r="883" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="883" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A883" s="15" t="s">
         <v>5605</v>
       </c>
@@ -66688,7 +66760,7 @@
         <v>欧阳茜茜</v>
       </c>
     </row>
-    <row r="884" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="884" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A884" s="15" t="s">
         <v>5611</v>
       </c>
@@ -66722,7 +66794,7 @@
         <v/>
       </c>
     </row>
-    <row r="885" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="885" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A885" s="15" t="s">
         <v>5615</v>
       </c>
@@ -66760,7 +66832,7 @@
         <v/>
       </c>
     </row>
-    <row r="886" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="886" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A886" s="15" t="s">
         <v>5621</v>
       </c>
@@ -66798,7 +66870,7 @@
         <v/>
       </c>
     </row>
-    <row r="887" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="887" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A887" s="15" t="s">
         <v>5627</v>
       </c>
@@ -66832,7 +66904,7 @@
         <v/>
       </c>
     </row>
-    <row r="888" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="888" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A888" s="15" t="s">
         <v>5631</v>
       </c>
@@ -66878,7 +66950,7 @@
         <v>伍嘉欣 伍友谊</v>
       </c>
     </row>
-    <row r="889" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="889" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A889" s="15" t="s">
         <v>5639</v>
       </c>
@@ -66924,7 +66996,7 @@
         <v>肖金先 汤美兰</v>
       </c>
     </row>
-    <row r="890" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="890" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A890" s="15" t="s">
         <v>5647</v>
       </c>
@@ -66966,7 +67038,7 @@
         <v>刘兰</v>
       </c>
     </row>
-    <row r="891" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="891" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A891" s="15" t="s">
         <v>5652</v>
       </c>
@@ -67008,7 +67080,7 @@
         <v>彭四明</v>
       </c>
     </row>
-    <row r="892" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="892" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A892" s="15" t="s">
         <v>5656</v>
       </c>
@@ -67052,7 +67124,7 @@
         <v>陈莉莉 李东明</v>
       </c>
     </row>
-    <row r="893" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="893" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A893" s="15" t="s">
         <v>5664</v>
       </c>
@@ -67090,7 +67162,7 @@
         <v/>
       </c>
     </row>
-    <row r="894" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="894" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A894" s="15" t="s">
         <v>5670</v>
       </c>
@@ -67132,7 +67204,7 @@
         <v>林星鑫</v>
       </c>
     </row>
-    <row r="895" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="895" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A895" s="15" t="s">
         <v>5676</v>
       </c>
@@ -67180,7 +67252,7 @@
         <v>黎萍平 晏财轩</v>
       </c>
     </row>
-    <row r="896" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="896" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A896" s="15" t="s">
         <v>5685</v>
       </c>
@@ -67214,7 +67286,7 @@
         <v/>
       </c>
     </row>
-    <row r="897" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="897" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A897" s="15" t="s">
         <v>5689</v>
       </c>
@@ -67248,7 +67320,7 @@
         <v/>
       </c>
     </row>
-    <row r="898" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="898" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A898" s="15" t="s">
         <v>5693</v>
       </c>
@@ -67282,7 +67354,7 @@
         <v/>
       </c>
     </row>
-    <row r="899" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="899" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A899" s="15" t="s">
         <v>5697</v>
       </c>
@@ -67328,7 +67400,7 @@
         <v>陈小强 王青梅</v>
       </c>
     </row>
-    <row r="900" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="900" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A900" s="15" t="s">
         <v>5705</v>
       </c>
@@ -67374,7 +67446,7 @@
         <v>肖基森 刘小英</v>
       </c>
     </row>
-    <row r="901" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="901" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A901" s="15" t="s">
         <v>5714</v>
       </c>
@@ -67420,7 +67492,7 @@
         <v>余丽华 林永根</v>
       </c>
     </row>
-    <row r="902" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="902" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A902" s="15" t="s">
         <v>5723</v>
       </c>
@@ -67466,7 +67538,7 @@
         <v>刘金龙 杨欢</v>
       </c>
     </row>
-    <row r="903" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="903" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A903" s="15" t="s">
         <v>5730</v>
       </c>
@@ -67514,7 +67586,7 @@
         <v>刘自铮 刘美琴</v>
       </c>
     </row>
-    <row r="904" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="904" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A904" s="15" t="s">
         <v>5739</v>
       </c>
@@ -67548,7 +67620,7 @@
         <v/>
       </c>
     </row>
-    <row r="905" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="905" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A905" s="15" t="s">
         <v>5743</v>
       </c>
@@ -67596,7 +67668,7 @@
         <v>马春香 刘懿昌</v>
       </c>
     </row>
-    <row r="906" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="906" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A906" s="15" t="s">
         <v>5752</v>
       </c>
@@ -67636,7 +67708,7 @@
         <v>王柏林</v>
       </c>
     </row>
-    <row r="907" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="907" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A907" s="15" t="s">
         <v>5758</v>
       </c>
@@ -67676,7 +67748,7 @@
         <v>王靖瑶</v>
       </c>
     </row>
-    <row r="908" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="908" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A908" s="15" t="s">
         <v>5764</v>
       </c>
@@ -67720,7 +67792,7 @@
         <v>罗玉琴 杨忠燕</v>
       </c>
     </row>
-    <row r="909" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="909" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A909" s="15" t="s">
         <v>5772</v>
       </c>
@@ -67760,7 +67832,7 @@
         <v>肖杨杰</v>
       </c>
     </row>
-    <row r="910" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="910" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A910" s="15" t="s">
         <v>5778</v>
       </c>
@@ -67804,7 +67876,7 @@
         <v>王敏 刘长生</v>
       </c>
     </row>
-    <row r="911" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="911" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A911" s="15" t="s">
         <v>5785</v>
       </c>
@@ -67844,7 +67916,7 @@
         <v>周遇平</v>
       </c>
     </row>
-    <row r="912" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="912" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A912" s="15" t="s">
         <v>5791</v>
       </c>
@@ -67882,7 +67954,7 @@
         <v/>
       </c>
     </row>
-    <row r="913" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="913" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A913" s="15" t="s">
         <v>5797</v>
       </c>
@@ -67920,7 +67992,7 @@
         <v/>
       </c>
     </row>
-    <row r="914" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="914" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A914" s="15" t="s">
         <v>5803</v>
       </c>
@@ -67952,7 +68024,7 @@
         <v/>
       </c>
     </row>
-    <row r="915" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="915" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A915" s="15" t="s">
         <v>5806</v>
       </c>
@@ -67990,7 +68062,7 @@
         <v/>
       </c>
     </row>
-    <row r="916" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="916" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A916" s="15" t="s">
         <v>5812</v>
       </c>
@@ -68028,7 +68100,7 @@
         <v/>
       </c>
     </row>
-    <row r="917" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="917" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A917" s="15" t="s">
         <v>5817</v>
       </c>
@@ -68066,7 +68138,7 @@
         <v/>
       </c>
     </row>
-    <row r="918" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="918" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A918" s="15" t="s">
         <v>5823</v>
       </c>
@@ -68104,7 +68176,7 @@
         <v/>
       </c>
     </row>
-    <row r="919" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="919" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A919" s="15" t="s">
         <v>5829</v>
       </c>
@@ -68142,7 +68214,7 @@
         <v/>
       </c>
     </row>
-    <row r="920" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="920" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A920" s="15" t="s">
         <v>5835</v>
       </c>
@@ -68180,7 +68252,7 @@
         <v/>
       </c>
     </row>
-    <row r="921" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="921" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A921" s="15" t="s">
         <v>5841</v>
       </c>
@@ -68214,7 +68286,7 @@
         <v/>
       </c>
     </row>
-    <row r="922" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="922" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A922" s="15" t="s">
         <v>5845</v>
       </c>
@@ -68256,7 +68328,7 @@
         <v>孙雅丽</v>
       </c>
     </row>
-    <row r="923" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="923" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A923" s="15" t="s">
         <v>5851</v>
       </c>
@@ -68303,7 +68375,7 @@
 刘威</v>
       </c>
     </row>
-    <row r="924" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
+    <row r="924" spans="1:15" ht="54" x14ac:dyDescent="0.15">
       <c r="A924" s="15" t="s">
         <v>5858</v>
       </c>
@@ -68351,7 +68423,7 @@
         <v>曾晓娇 刘达钴</v>
       </c>
     </row>
-    <row r="925" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="925" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A925" s="15" t="s">
         <v>5867</v>
       </c>
@@ -68383,7 +68455,7 @@
       <c r="M925" s="15"/>
       <c r="N925" s="15"/>
     </row>
-    <row r="926" spans="1:15" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="926" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A926" s="15" t="s">
         <v>5872</v>
       </c>
@@ -68413,7 +68485,7 @@
       <c r="M926" s="15"/>
       <c r="N926" s="15"/>
     </row>
-    <row r="927" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="927" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A927" s="15" t="s">
         <v>5876</v>
       </c>
@@ -68525,7 +68597,7 @@
         <v>周静</v>
       </c>
     </row>
-    <row r="930" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="930" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A930" s="15" t="s">
         <v>5893</v>
       </c>
@@ -68563,7 +68635,7 @@
         <v/>
       </c>
     </row>
-    <row r="931" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="931" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A931" s="15" t="s">
         <v>5899</v>
       </c>
@@ -68597,7 +68669,7 @@
       <c r="M931" s="15"/>
       <c r="N931" s="15"/>
     </row>
-    <row r="932" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="932" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A932" s="15" t="s">
         <v>5905</v>
       </c>
@@ -68631,7 +68703,7 @@
       <c r="M932" s="15"/>
       <c r="N932" s="15"/>
     </row>
-    <row r="933" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="933" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A933" s="15" t="s">
         <v>5911</v>
       </c>
@@ -68659,7 +68731,7 @@
       <c r="M933" s="15"/>
       <c r="N933" s="15"/>
     </row>
-    <row r="934" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="934" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A934" s="15" t="s">
         <v>5915</v>
       </c>
@@ -68701,7 +68773,7 @@
         <v>吴梅香</v>
       </c>
     </row>
-    <row r="935" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="935" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A935" s="15" t="s">
         <v>5921</v>
       </c>
@@ -68739,7 +68811,7 @@
         <v/>
       </c>
     </row>
-    <row r="936" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="936" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A936" s="15" t="s">
         <v>5927</v>
       </c>
@@ -68777,7 +68849,7 @@
         <v/>
       </c>
     </row>
-    <row r="937" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="937" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A937" s="15" t="s">
         <v>5933</v>
       </c>
@@ -68817,7 +68889,7 @@
         <v>熊泽东</v>
       </c>
     </row>
-    <row r="938" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="938" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A938" s="15" t="s">
         <v>5939</v>
       </c>
@@ -68865,7 +68937,7 @@
         <v>周春根 罗玲</v>
       </c>
     </row>
-    <row r="939" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="939" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A939" s="15" t="s">
         <v>5948</v>
       </c>
@@ -68907,7 +68979,7 @@
         <v>吴香香</v>
       </c>
     </row>
-    <row r="940" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="940" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A940" s="15" t="s">
         <v>5954</v>
       </c>
@@ -68953,7 +69025,7 @@
         <v>李根香 陈伟</v>
       </c>
     </row>
-    <row r="941" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="941" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A941" s="15" t="s">
         <v>5961</v>
       </c>
@@ -69001,7 +69073,7 @@
         <v>曹检英 曾传蕊</v>
       </c>
     </row>
-    <row r="942" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="942" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A942" s="15" t="s">
         <v>5970</v>
       </c>
@@ -69043,7 +69115,7 @@
         <v>罗根秀</v>
       </c>
     </row>
-    <row r="943" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="943" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A943" s="15" t="s">
         <v>5976</v>
       </c>
@@ -69081,7 +69153,7 @@
         <v/>
       </c>
     </row>
-    <row r="944" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="944" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A944" s="15" t="s">
         <v>5982</v>
       </c>
@@ -69119,7 +69191,7 @@
         <v/>
       </c>
     </row>
-    <row r="945" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="945" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A945" s="15" t="s">
         <v>5988</v>
       </c>
@@ -69167,7 +69239,7 @@
         <v>刘国丰 王桂花</v>
       </c>
     </row>
-    <row r="946" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="946" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A946" s="15" t="s">
         <v>5997</v>
       </c>
@@ -69211,7 +69283,7 @@
         <v>王婷 陈柳茂</v>
       </c>
     </row>
-    <row r="947" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="947" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A947" s="15" t="s">
         <v>6004</v>
       </c>
@@ -69255,7 +69327,7 @@
         <v>黄富才 陈小艳</v>
       </c>
     </row>
-    <row r="948" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="948" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A948" s="15" t="s">
         <v>6012</v>
       </c>
@@ -69299,7 +69371,7 @@
         <v>罗艳 焦建平</v>
       </c>
     </row>
-    <row r="949" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="949" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A949" s="15" t="s">
         <v>6020</v>
       </c>
@@ -69343,7 +69415,7 @@
         <v>康康 罗兰英</v>
       </c>
     </row>
-    <row r="950" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="950" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A950" s="15" t="s">
         <v>6028</v>
       </c>
@@ -69387,7 +69459,7 @@
         <v>刘小芳 张振明</v>
       </c>
     </row>
-    <row r="951" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="951" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A951" s="15" t="s">
         <v>6035</v>
       </c>
@@ -69421,7 +69493,7 @@
         <v/>
       </c>
     </row>
-    <row r="952" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="952" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A952" s="15" t="s">
         <v>6039</v>
       </c>
@@ -69459,7 +69531,7 @@
         <v/>
       </c>
     </row>
-    <row r="953" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="953" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A953" s="15" t="s">
         <v>6045</v>
       </c>
@@ -69497,7 +69569,7 @@
         <v/>
       </c>
     </row>
-    <row r="954" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="954" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A954" s="15" t="s">
         <v>6051</v>
       </c>
@@ -69531,7 +69603,7 @@
         <v/>
       </c>
     </row>
-    <row r="955" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="955" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A955" s="15" t="s">
         <v>6055</v>
       </c>
@@ -69569,7 +69641,7 @@
         <v/>
       </c>
     </row>
-    <row r="956" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="956" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A956" s="15" t="s">
         <v>6061</v>
       </c>
@@ -69607,7 +69679,7 @@
         <v/>
       </c>
     </row>
-    <row r="957" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="957" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A957" s="15" t="s">
         <v>6067</v>
       </c>
@@ -69645,7 +69717,7 @@
         <v/>
       </c>
     </row>
-    <row r="958" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="958" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A958" s="15" t="s">
         <v>6073</v>
       </c>
@@ -69683,7 +69755,7 @@
         <v/>
       </c>
     </row>
-    <row r="959" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="959" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A959" s="15" t="s">
         <v>6079</v>
       </c>
@@ -69721,7 +69793,7 @@
         <v/>
       </c>
     </row>
-    <row r="960" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="960" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A960" s="15" t="s">
         <v>6085</v>
       </c>
@@ -69759,7 +69831,7 @@
         <v/>
       </c>
     </row>
-    <row r="961" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="961" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A961" s="15" t="s">
         <v>6091</v>
       </c>
@@ -69801,7 +69873,7 @@
         <v>孙玥澜</v>
       </c>
     </row>
-    <row r="962" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="962" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A962" s="15" t="s">
         <v>6097</v>
       </c>
@@ -69843,7 +69915,7 @@
         <v>肖利剑</v>
       </c>
     </row>
-    <row r="963" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="963" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A963" s="15" t="s">
         <v>6103</v>
       </c>
@@ -69891,7 +69963,7 @@
         <v>袁玲根 刘芳芳</v>
       </c>
     </row>
-    <row r="964" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="964" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A964" s="15" t="s">
         <v>6112</v>
       </c>
@@ -69933,7 +70005,7 @@
         <v>罗娇</v>
       </c>
     </row>
-    <row r="965" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="965" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A965" s="15" t="s">
         <v>6118</v>
       </c>
@@ -69967,7 +70039,7 @@
         <v/>
       </c>
     </row>
-    <row r="966" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="966" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A966" s="15" t="s">
         <v>6122</v>
       </c>
@@ -70009,7 +70081,7 @@
         <v>周健</v>
       </c>
     </row>
-    <row r="967" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="967" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A967" s="15" t="s">
         <v>6125</v>
       </c>
@@ -70053,7 +70125,7 @@
         <v>徐爱珍 梁传兵</v>
       </c>
     </row>
-    <row r="968" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="968" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A968" s="15" t="s">
         <v>6133</v>
       </c>
@@ -70097,7 +70169,7 @@
         <v>王凤英 彭九根</v>
       </c>
     </row>
-    <row r="969" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="969" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A969" s="15" t="s">
         <v>6141</v>
       </c>
@@ -70137,7 +70209,7 @@
         <v>刘永强</v>
       </c>
     </row>
-    <row r="970" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="970" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A970" s="15" t="s">
         <v>6147</v>
       </c>
@@ -70185,7 +70257,7 @@
         <v>匡贤缙 陆柳芬</v>
       </c>
     </row>
-    <row r="971" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="971" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A971" s="18" t="s">
         <v>6156</v>
       </c>
@@ -70229,7 +70301,7 @@
         <v>杨元福 王丹</v>
       </c>
     </row>
-    <row r="972" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="972" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A972" s="15" t="s">
         <v>6165</v>
       </c>
@@ -70273,7 +70345,7 @@
         <v>汪利红 尹艳平</v>
       </c>
     </row>
-    <row r="973" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="973" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A973" s="18" t="s">
         <v>6156</v>
       </c>
@@ -70311,7 +70383,7 @@
         <v>刘未</v>
       </c>
     </row>
-    <row r="974" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="974" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A974" s="15"/>
       <c r="B974" s="6" t="s">
         <v>6178</v>
@@ -70349,7 +70421,7 @@
         <v/>
       </c>
     </row>
-    <row r="975" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="975" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A975" s="15" t="s">
         <v>6183</v>
       </c>
@@ -70383,7 +70455,7 @@
         <v/>
       </c>
     </row>
-    <row r="976" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="976" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A976" s="15" t="s">
         <v>6187</v>
       </c>
@@ -70421,7 +70493,7 @@
         <v/>
       </c>
     </row>
-    <row r="977" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="977" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A977" s="15" t="s">
         <v>6193</v>
       </c>
@@ -70469,7 +70541,7 @@
         <v>李潘兰 邓相华</v>
       </c>
     </row>
-    <row r="978" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="978" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A978" s="15" t="s">
         <v>6202</v>
       </c>
@@ -70517,7 +70589,7 @@
         <v>舒惠能 余红</v>
       </c>
     </row>
-    <row r="979" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="979" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A979" s="15" t="s">
         <v>6211</v>
       </c>
@@ -70557,7 +70629,7 @@
         <v>邓娟娟</v>
       </c>
     </row>
-    <row r="980" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="980" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A980" s="15" t="s">
         <v>6217</v>
       </c>
@@ -70605,7 +70677,7 @@
         <v>林冬梅 龙春仁</v>
       </c>
     </row>
-    <row r="981" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
+    <row r="981" spans="1:15" ht="27" x14ac:dyDescent="0.15">
       <c r="A981" s="30" t="s">
         <v>6217</v>
       </c>
@@ -75001,4 +75073,568 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0675D2-49C3-460E-8DE0-600D1D45FF16}">
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="12.75" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.625" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A1" s="36"/>
+      <c r="B1" s="37" t="s">
+        <v>6566</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>6574</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>535</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>6571</v>
+      </c>
+      <c r="G1" s="36" t="s">
+        <v>528</v>
+      </c>
+      <c r="H1" s="36"/>
+      <c r="I1" s="19"/>
+    </row>
+    <row r="2" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A2" s="36" t="s">
+        <v>6575</v>
+      </c>
+      <c r="B2" s="36">
+        <v>1</v>
+      </c>
+      <c r="C2" s="36">
+        <v>1</v>
+      </c>
+      <c r="D2" s="36">
+        <v>1</v>
+      </c>
+      <c r="E2" s="36">
+        <v>1</v>
+      </c>
+      <c r="F2" s="36">
+        <v>1</v>
+      </c>
+      <c r="G2" s="36">
+        <v>1</v>
+      </c>
+      <c r="H2" s="36"/>
+      <c r="I2" s="19"/>
+    </row>
+    <row r="3" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A3" s="37" t="s">
+        <v>6576</v>
+      </c>
+      <c r="B3" s="37">
+        <v>1</v>
+      </c>
+      <c r="C3" s="37">
+        <v>1</v>
+      </c>
+      <c r="D3" s="36">
+        <v>1</v>
+      </c>
+      <c r="E3" s="36">
+        <v>1</v>
+      </c>
+      <c r="F3" s="36">
+        <v>0</v>
+      </c>
+      <c r="G3" s="35">
+        <v>0</v>
+      </c>
+      <c r="H3" s="36"/>
+      <c r="I3" s="19"/>
+    </row>
+    <row r="4" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A4" s="37" t="s">
+        <v>6577</v>
+      </c>
+      <c r="B4" s="37">
+        <v>1</v>
+      </c>
+      <c r="C4" s="37">
+        <v>1</v>
+      </c>
+      <c r="D4" s="36">
+        <v>1</v>
+      </c>
+      <c r="E4" s="36">
+        <v>1</v>
+      </c>
+      <c r="F4" s="36">
+        <v>1</v>
+      </c>
+      <c r="G4" s="35">
+        <v>1</v>
+      </c>
+      <c r="H4" s="36"/>
+      <c r="I4" s="19"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A5" s="37" t="s">
+        <v>6578</v>
+      </c>
+      <c r="B5" s="37">
+        <v>1</v>
+      </c>
+      <c r="C5" s="37">
+        <v>1</v>
+      </c>
+      <c r="D5" s="36">
+        <v>1</v>
+      </c>
+      <c r="E5" s="36">
+        <v>1</v>
+      </c>
+      <c r="F5" s="36">
+        <v>1</v>
+      </c>
+      <c r="G5" s="35">
+        <v>1</v>
+      </c>
+      <c r="H5" s="36"/>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A6" s="37" t="s">
+        <v>6585</v>
+      </c>
+      <c r="B6" s="37">
+        <v>0</v>
+      </c>
+      <c r="C6" s="37">
+        <v>0</v>
+      </c>
+      <c r="D6" s="36">
+        <v>1</v>
+      </c>
+      <c r="E6" s="36">
+        <v>0</v>
+      </c>
+      <c r="F6" s="36">
+        <v>0</v>
+      </c>
+      <c r="G6" s="35">
+        <v>0</v>
+      </c>
+      <c r="H6" s="36"/>
+      <c r="I6" s="19"/>
+    </row>
+    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A7" s="37" t="s">
+        <v>6584</v>
+      </c>
+      <c r="B7" s="37">
+        <v>0</v>
+      </c>
+      <c r="C7" s="37">
+        <v>0</v>
+      </c>
+      <c r="D7" s="36">
+        <v>0</v>
+      </c>
+      <c r="E7" s="36">
+        <v>1</v>
+      </c>
+      <c r="F7" s="36">
+        <v>1</v>
+      </c>
+      <c r="G7" s="35">
+        <v>1</v>
+      </c>
+      <c r="H7" s="36"/>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A8" s="37" t="s">
+        <v>6583</v>
+      </c>
+      <c r="B8" s="37">
+        <v>1</v>
+      </c>
+      <c r="C8" s="37">
+        <v>1</v>
+      </c>
+      <c r="D8" s="36">
+        <v>0</v>
+      </c>
+      <c r="E8" s="36">
+        <v>1</v>
+      </c>
+      <c r="F8" s="36">
+        <v>0</v>
+      </c>
+      <c r="G8" s="35">
+        <v>1</v>
+      </c>
+      <c r="H8" s="36"/>
+      <c r="I8" s="19"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A9" s="37" t="s">
+        <v>6581</v>
+      </c>
+      <c r="B9" s="36">
+        <v>1</v>
+      </c>
+      <c r="C9" s="37">
+        <v>1</v>
+      </c>
+      <c r="D9" s="36">
+        <v>1</v>
+      </c>
+      <c r="E9" s="36">
+        <v>0</v>
+      </c>
+      <c r="F9" s="36">
+        <v>0</v>
+      </c>
+      <c r="G9" s="35">
+        <v>0</v>
+      </c>
+      <c r="H9" s="36"/>
+      <c r="I9" s="19"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A10" s="37" t="s">
+        <v>6582</v>
+      </c>
+      <c r="B10" s="36">
+        <v>0</v>
+      </c>
+      <c r="C10" s="37">
+        <v>1</v>
+      </c>
+      <c r="D10" s="36">
+        <v>0</v>
+      </c>
+      <c r="E10" s="36">
+        <v>0</v>
+      </c>
+      <c r="F10" s="36">
+        <v>0</v>
+      </c>
+      <c r="G10" s="37">
+        <v>0</v>
+      </c>
+      <c r="H10" s="36"/>
+      <c r="I10" s="19"/>
+    </row>
+    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A11" s="37" t="s">
+        <v>6580</v>
+      </c>
+      <c r="B11" s="36">
+        <v>0</v>
+      </c>
+      <c r="C11" s="37">
+        <v>0</v>
+      </c>
+      <c r="D11" s="36">
+        <v>0</v>
+      </c>
+      <c r="E11" s="36">
+        <v>0</v>
+      </c>
+      <c r="F11" s="36">
+        <v>1</v>
+      </c>
+      <c r="G11" s="37">
+        <v>1</v>
+      </c>
+      <c r="H11" s="36"/>
+      <c r="I11" s="19"/>
+    </row>
+    <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A12" s="37" t="s">
+        <v>6586</v>
+      </c>
+      <c r="B12" s="36">
+        <v>0</v>
+      </c>
+      <c r="C12" s="37">
+        <v>0</v>
+      </c>
+      <c r="D12" s="36">
+        <v>1</v>
+      </c>
+      <c r="E12" s="36">
+        <v>0</v>
+      </c>
+      <c r="F12" s="36">
+        <v>0</v>
+      </c>
+      <c r="G12" s="37">
+        <v>0</v>
+      </c>
+      <c r="H12" s="36"/>
+      <c r="I12" s="19"/>
+    </row>
+    <row r="13" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A13" s="37" t="s">
+        <v>6587</v>
+      </c>
+      <c r="B13" s="36">
+        <v>0</v>
+      </c>
+      <c r="C13" s="37">
+        <v>0</v>
+      </c>
+      <c r="D13" s="36">
+        <v>1</v>
+      </c>
+      <c r="E13" s="36">
+        <v>0</v>
+      </c>
+      <c r="F13" s="36">
+        <v>0</v>
+      </c>
+      <c r="G13" s="37">
+        <v>0</v>
+      </c>
+      <c r="H13" s="36"/>
+      <c r="I13" s="19"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A14" s="37" t="s">
+        <v>6579</v>
+      </c>
+      <c r="B14" s="37">
+        <v>1</v>
+      </c>
+      <c r="C14" s="37">
+        <v>1</v>
+      </c>
+      <c r="D14" s="36">
+        <v>1</v>
+      </c>
+      <c r="E14" s="36">
+        <v>1</v>
+      </c>
+      <c r="F14" s="36">
+        <v>1</v>
+      </c>
+      <c r="G14" s="36">
+        <v>1</v>
+      </c>
+      <c r="H14" s="36"/>
+      <c r="I14" s="19"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A15" s="37" t="s">
+        <v>6588</v>
+      </c>
+      <c r="B15" s="36">
+        <f>SUM(B2:B14)</f>
+        <v>7</v>
+      </c>
+      <c r="C15" s="36">
+        <f t="shared" ref="C15:G15" si="0">SUM(C2:C14)</f>
+        <v>8</v>
+      </c>
+      <c r="D15" s="36">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="E15" s="36">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F15" s="36">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G15" s="36">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H15" s="36"/>
+      <c r="I15" s="19"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A16" s="36"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="19"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A17" s="36"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="19"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A18" s="36"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="19"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="19"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A20" s="36"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="19"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/文档及测试数据/抵押登记台账.xlsx
+++ b/文档及测试数据/抵押登记台账.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LCY\AppData\Roaming\SPB_Data\gitee\auto-work\文档及测试数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LCY\gitee\auto-work\文档及测试数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4DE054-4640-49D0-A039-6FBD873341D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939F6946-9903-47A7-A88D-3DACD7FDDA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14355" yWindow="5475" windowWidth="21945" windowHeight="14100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2310" windowWidth="27705" windowHeight="16260" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="预告抵押（合并登记）" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9991" uniqueCount="6589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9993" uniqueCount="6591">
   <si>
     <t>登记业务号</t>
   </si>
@@ -21868,9 +21868,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>不动产登记申请书</t>
-  </si>
-  <si>
     <t>不动产抵押登记询问笔录</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -21919,7 +21916,19 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>求和</t>
+    <t>不动产登记申请书</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>imagetype</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pledgetype</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pledge_img_info</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -22137,8 +22146,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -75077,74 +75086,79 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0675D2-49C3-460E-8DE0-600D1D45FF16}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.75" customWidth="1"/>
-    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.625" customWidth="1"/>
-    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" customWidth="1"/>
+    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="36"/>
-      <c r="B1" s="37" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A1" s="38" t="s">
+        <v>6590</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>6589</v>
+      </c>
+      <c r="C1">
+        <v>1</v>
+      </c>
+      <c r="D1">
+        <v>2</v>
+      </c>
+      <c r="E1">
+        <v>3</v>
+      </c>
+      <c r="F1">
+        <v>4</v>
+      </c>
+      <c r="G1">
+        <v>5</v>
+      </c>
+      <c r="H1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A2" s="38" t="s">
+        <v>6588</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="37" t="s">
         <v>6566</v>
       </c>
-      <c r="C1" s="36" t="s">
-        <v>509</v>
-      </c>
-      <c r="D1" s="38" t="s">
+      <c r="D2" s="37" t="s">
+        <v>6567</v>
+      </c>
+      <c r="E2" s="36" t="s">
         <v>6574</v>
       </c>
-      <c r="E1" s="36" t="s">
-        <v>535</v>
-      </c>
-      <c r="F1" s="37" t="s">
+      <c r="F2" s="37" t="s">
+        <v>6569</v>
+      </c>
+      <c r="G2" s="37" t="s">
         <v>6571</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="H2" s="36" t="s">
         <v>528</v>
       </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="19"/>
-    </row>
-    <row r="2" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
-      <c r="A2" s="36" t="s">
-        <v>6575</v>
-      </c>
-      <c r="B2" s="36">
+      <c r="I2" s="36"/>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="C2" s="36">
-        <v>1</v>
-      </c>
-      <c r="D2" s="36">
-        <v>1</v>
-      </c>
-      <c r="E2" s="36">
-        <v>1</v>
-      </c>
-      <c r="F2" s="36">
-        <v>1</v>
-      </c>
-      <c r="G2" s="36">
-        <v>1</v>
-      </c>
-      <c r="H2" s="36"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
-      <c r="A3" s="37" t="s">
-        <v>6576</v>
-      </c>
-      <c r="B3" s="37">
-        <v>1</v>
-      </c>
-      <c r="C3" s="37">
+      <c r="B3" s="37" t="s">
+        <v>6587</v>
+      </c>
+      <c r="C3" s="36">
         <v>1</v>
       </c>
       <c r="D3" s="36">
@@ -75154,25 +75168,28 @@
         <v>1</v>
       </c>
       <c r="F3" s="36">
-        <v>0</v>
-      </c>
-      <c r="G3" s="35">
-        <v>0</v>
-      </c>
-      <c r="H3" s="36"/>
-      <c r="I3" s="19"/>
-    </row>
-    <row r="4" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
-      <c r="A4" s="37" t="s">
-        <v>6577</v>
-      </c>
-      <c r="B4" s="37">
         <v>1</v>
+      </c>
+      <c r="G3" s="36">
+        <v>1</v>
+      </c>
+      <c r="H3" s="36">
+        <v>1</v>
+      </c>
+      <c r="I3" s="36"/>
+      <c r="J3" s="19"/>
+    </row>
+    <row r="4" spans="1:10" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>6575</v>
       </c>
       <c r="C4" s="37">
         <v>1</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="37">
         <v>1</v>
       </c>
       <c r="E4" s="36">
@@ -75181,23 +75198,26 @@
       <c r="F4" s="36">
         <v>1</v>
       </c>
-      <c r="G4" s="35">
-        <v>1</v>
-      </c>
-      <c r="H4" s="36"/>
-      <c r="I4" s="19"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" s="37" t="s">
-        <v>6578</v>
-      </c>
-      <c r="B5" s="37">
-        <v>1</v>
+      <c r="G4" s="36">
+        <v>0</v>
+      </c>
+      <c r="H4" s="35">
+        <v>0</v>
+      </c>
+      <c r="I4" s="36"/>
+      <c r="J4" s="19"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>6576</v>
       </c>
       <c r="C5" s="37">
         <v>1</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="37">
         <v>1</v>
       </c>
       <c r="E5" s="36">
@@ -75206,174 +75226,195 @@
       <c r="F5" s="36">
         <v>1</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="36">
         <v>1</v>
       </c>
-      <c r="H5" s="36"/>
-      <c r="I5" s="19"/>
-    </row>
-    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="37" t="s">
-        <v>6585</v>
-      </c>
-      <c r="B6" s="37">
-        <v>0</v>
+      <c r="H5" s="35">
+        <v>1</v>
+      </c>
+      <c r="I5" s="36"/>
+      <c r="J5" s="19"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>6577</v>
       </c>
       <c r="C6" s="37">
-        <v>0</v>
-      </c>
-      <c r="D6" s="36">
         <v>1</v>
       </c>
+      <c r="D6" s="37">
+        <v>1</v>
+      </c>
       <c r="E6" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="36">
-        <v>0</v>
-      </c>
-      <c r="G6" s="35">
-        <v>0</v>
-      </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
-      <c r="A7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="36">
+        <v>1</v>
+      </c>
+      <c r="H6" s="35">
+        <v>1</v>
+      </c>
+      <c r="I6" s="36"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="37" t="s">
         <v>6584</v>
-      </c>
-      <c r="B7" s="37">
-        <v>0</v>
       </c>
       <c r="C7" s="37">
         <v>0</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="37">
         <v>0</v>
       </c>
       <c r="E7" s="36">
         <v>1</v>
       </c>
       <c r="F7" s="36">
+        <v>0</v>
+      </c>
+      <c r="G7" s="36">
+        <v>0</v>
+      </c>
+      <c r="H7" s="35">
+        <v>0</v>
+      </c>
+      <c r="I7" s="36"/>
+      <c r="J7" s="19"/>
+    </row>
+    <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>6583</v>
+      </c>
+      <c r="C8" s="37">
+        <v>0</v>
+      </c>
+      <c r="D8" s="37">
+        <v>0</v>
+      </c>
+      <c r="E8" s="36">
+        <v>0</v>
+      </c>
+      <c r="F8" s="36">
         <v>1</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G8" s="36">
         <v>1</v>
       </c>
-      <c r="H7" s="36"/>
-      <c r="I7" s="19"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A8" s="37" t="s">
-        <v>6583</v>
-      </c>
-      <c r="B8" s="37">
+      <c r="H8" s="35">
         <v>1</v>
       </c>
-      <c r="C8" s="37">
-        <v>1</v>
-      </c>
-      <c r="D8" s="36">
-        <v>0</v>
-      </c>
-      <c r="E8" s="36">
-        <v>1</v>
-      </c>
-      <c r="F8" s="36">
-        <v>0</v>
-      </c>
-      <c r="G8" s="35">
-        <v>1</v>
-      </c>
-      <c r="H8" s="36"/>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A9" s="37" t="s">
-        <v>6581</v>
-      </c>
-      <c r="B9" s="36">
-        <v>1</v>
+      <c r="I8" s="36"/>
+      <c r="J8" s="19"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>6582</v>
       </c>
       <c r="C9" s="37">
         <v>1</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="37">
         <v>1</v>
       </c>
       <c r="E9" s="36">
         <v>0</v>
       </c>
       <c r="F9" s="36">
+        <v>1</v>
+      </c>
+      <c r="G9" s="36">
         <v>0</v>
       </c>
-      <c r="G9" s="35">
-        <v>0</v>
-      </c>
-      <c r="H9" s="36"/>
-      <c r="I9" s="19"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A10" s="37" t="s">
-        <v>6582</v>
-      </c>
-      <c r="B10" s="36">
-        <v>0</v>
-      </c>
-      <c r="C10" s="37">
+      <c r="H9" s="35">
         <v>1</v>
       </c>
-      <c r="D10" s="36">
-        <v>0</v>
+      <c r="I9" s="36"/>
+      <c r="J9" s="19"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>6580</v>
+      </c>
+      <c r="C10" s="36">
+        <v>1</v>
+      </c>
+      <c r="D10" s="37">
+        <v>1</v>
       </c>
       <c r="E10" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="36">
         <v>0</v>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="36">
         <v>0</v>
       </c>
-      <c r="H10" s="36"/>
-      <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
-      <c r="A11" s="37" t="s">
-        <v>6580</v>
-      </c>
-      <c r="B11" s="36">
+      <c r="H10" s="35">
         <v>0</v>
       </c>
-      <c r="C11" s="37">
+      <c r="I10" s="36"/>
+      <c r="J10" s="19"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>6581</v>
+      </c>
+      <c r="C11" s="36">
         <v>0</v>
       </c>
-      <c r="D11" s="36">
-        <v>0</v>
+      <c r="D11" s="37">
+        <v>1</v>
       </c>
       <c r="E11" s="36">
         <v>0</v>
       </c>
       <c r="F11" s="36">
-        <v>1</v>
-      </c>
-      <c r="G11" s="37">
-        <v>1</v>
-      </c>
-      <c r="H11" s="36"/>
-      <c r="I11" s="19"/>
-    </row>
-    <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
-      <c r="A12" s="37" t="s">
-        <v>6586</v>
-      </c>
-      <c r="B12" s="36">
         <v>0</v>
       </c>
-      <c r="C12" s="37">
+      <c r="G11" s="36">
         <v>0</v>
       </c>
-      <c r="D12" s="36">
-        <v>1</v>
+      <c r="H11" s="37">
+        <v>0</v>
+      </c>
+      <c r="I11" s="36"/>
+      <c r="J11" s="19"/>
+    </row>
+    <row r="12" spans="1:10" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>6579</v>
+      </c>
+      <c r="C12" s="36">
+        <v>0</v>
+      </c>
+      <c r="D12" s="37">
+        <v>0</v>
       </c>
       <c r="E12" s="36">
         <v>0</v>
@@ -75381,161 +75422,169 @@
       <c r="F12" s="36">
         <v>0</v>
       </c>
-      <c r="G12" s="37">
+      <c r="G12" s="36">
+        <v>1</v>
+      </c>
+      <c r="H12" s="37">
+        <v>1</v>
+      </c>
+      <c r="I12" s="36"/>
+      <c r="J12" s="19"/>
+    </row>
+    <row r="13" spans="1:10" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>6585</v>
+      </c>
+      <c r="C13" s="36">
         <v>0</v>
       </c>
-      <c r="H12" s="36"/>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" ht="28.5" x14ac:dyDescent="0.15">
-      <c r="A13" s="37" t="s">
-        <v>6587</v>
-      </c>
-      <c r="B13" s="36">
+      <c r="D13" s="37">
         <v>0</v>
       </c>
-      <c r="C13" s="37">
-        <v>0</v>
-      </c>
-      <c r="D13" s="36">
+      <c r="E13" s="36">
         <v>1</v>
-      </c>
-      <c r="E13" s="36">
-        <v>0</v>
       </c>
       <c r="F13" s="36">
         <v>0</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <v>0</v>
       </c>
-      <c r="H13" s="36"/>
-      <c r="I13" s="19"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A14" s="37" t="s">
-        <v>6579</v>
-      </c>
-      <c r="B14" s="37">
-        <v>1</v>
-      </c>
-      <c r="C14" s="37">
-        <v>1</v>
-      </c>
-      <c r="D14" s="36">
-        <v>1</v>
+      <c r="H13" s="37">
+        <v>0</v>
+      </c>
+      <c r="I13" s="36"/>
+      <c r="J13" s="19"/>
+    </row>
+    <row r="14" spans="1:10" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>6586</v>
+      </c>
+      <c r="C14" s="36">
+        <v>0</v>
+      </c>
+      <c r="D14" s="37">
+        <v>0</v>
       </c>
       <c r="E14" s="36">
         <v>1</v>
       </c>
       <c r="F14" s="36">
+        <v>0</v>
+      </c>
+      <c r="G14" s="36">
+        <v>0</v>
+      </c>
+      <c r="H14" s="37">
+        <v>0</v>
+      </c>
+      <c r="I14" s="36"/>
+      <c r="J14" s="19"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>6578</v>
+      </c>
+      <c r="C15" s="37">
         <v>1</v>
       </c>
-      <c r="G14" s="36">
+      <c r="D15" s="37">
         <v>1</v>
       </c>
-      <c r="H14" s="36"/>
-      <c r="I14" s="19"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A15" s="37" t="s">
-        <v>6588</v>
-      </c>
-      <c r="B15" s="36">
-        <f>SUM(B2:B14)</f>
-        <v>7</v>
-      </c>
-      <c r="C15" s="36">
-        <f t="shared" ref="C15:G15" si="0">SUM(C2:C14)</f>
-        <v>8</v>
-      </c>
-      <c r="D15" s="36">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
       <c r="E15" s="36">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F15" s="36">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G15" s="36">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="H15" s="36"/>
-      <c r="I15" s="19"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A16" s="36"/>
+        <v>1</v>
+      </c>
+      <c r="H15" s="36">
+        <v>1</v>
+      </c>
+      <c r="I15" s="36"/>
+      <c r="J15" s="19"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
+      <c r="C16" s="36" t="str">
+        <f>"["&amp;C1&amp;"]="</f>
+        <v>[1]=</v>
+      </c>
       <c r="D16" s="36"/>
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
       <c r="G16" s="36"/>
       <c r="H16" s="36"/>
-      <c r="I16" s="19"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A17" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="19"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="19"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A18" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B18" s="36"/>
       <c r="C18" s="36"/>
       <c r="D18" s="36"/>
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A19" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="19"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B19" s="36"/>
       <c r="C19" s="36"/>
       <c r="D19" s="36"/>
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="19"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A20" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="19"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B20" s="36"/>
       <c r="C20" s="36"/>
       <c r="D20" s="36"/>
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="19"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A21" s="19"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="19"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
       <c r="F21" s="19"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="37"/>
       <c r="I21" s="19"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A22" s="19"/>
+      <c r="J21" s="19"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -75544,9 +75593,9 @@
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A23" s="19"/>
+      <c r="J22" s="19"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
@@ -75555,9 +75604,9 @@
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A24" s="19"/>
+      <c r="J23" s="19"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
@@ -75566,9 +75615,9 @@
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A25" s="19"/>
+      <c r="J24" s="19"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
@@ -75577,9 +75626,9 @@
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A26" s="19"/>
+      <c r="J25" s="19"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
       <c r="D26" s="19"/>
@@ -75588,9 +75637,9 @@
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A27" s="19"/>
+      <c r="J26" s="19"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
@@ -75599,9 +75648,9 @@
       <c r="G27" s="19"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A28" s="19"/>
+      <c r="J27" s="19"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -75610,9 +75659,9 @@
       <c r="G28" s="19"/>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A29" s="19"/>
+      <c r="J28" s="19"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
@@ -75621,9 +75670,9 @@
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A30" s="19"/>
+      <c r="J29" s="19"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
@@ -75632,9 +75681,11 @@
       <c r="G30" s="19"/>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>